--- a/MetaEdOutput/Documentation/DataDictionary/XmlDataDictionary.xlsx
+++ b/MetaEdOutput/Documentation/DataDictionary/XmlDataDictionary.xlsx
@@ -45312,7 +45312,7 @@
         <v>2970</v>
       </c>
       <c r="C1924" t="s">
-        <v>61</v>
+        <v>1460</v>
       </c>
       <c r="D1924" t="s">
         <v>8</v>
@@ -45329,7 +45329,7 @@
         <v>2970</v>
       </c>
       <c r="C1925" t="s">
-        <v>966</v>
+        <v>1388</v>
       </c>
       <c r="D1925" t="s">
         <v>8</v>
@@ -45346,7 +45346,7 @@
         <v>2970</v>
       </c>
       <c r="C1926" t="s">
-        <v>1581</v>
+        <v>452</v>
       </c>
       <c r="D1926" t="s">
         <v>8</v>
@@ -45363,7 +45363,7 @@
         <v>2970</v>
       </c>
       <c r="C1927" t="s">
-        <v>1178</v>
+        <v>61</v>
       </c>
       <c r="D1927" t="s">
         <v>8</v>
@@ -45380,7 +45380,7 @@
         <v>2970</v>
       </c>
       <c r="C1928" t="s">
-        <v>1631</v>
+        <v>966</v>
       </c>
       <c r="D1928" t="s">
         <v>8</v>
@@ -45397,7 +45397,7 @@
         <v>2970</v>
       </c>
       <c r="C1929" t="s">
-        <v>1598</v>
+        <v>1581</v>
       </c>
       <c r="D1929" t="s">
         <v>8</v>
@@ -45414,7 +45414,7 @@
         <v>2970</v>
       </c>
       <c r="C1930" t="s">
-        <v>1632</v>
+        <v>1178</v>
       </c>
       <c r="D1930" t="s">
         <v>8</v>
@@ -45425,801 +45425,801 @@
     </row>
     <row r="1931">
       <c r="A1931" t="s">
-        <v>3027</v>
+        <v>3003</v>
       </c>
       <c r="B1931" t="s">
-        <v>1287</v>
+        <v>2970</v>
       </c>
       <c r="C1931" t="s">
-        <v>3028</v>
+        <v>1608</v>
       </c>
       <c r="D1931" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1931" t="s">
-        <v>3029</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1932">
       <c r="A1932" t="s">
-        <v>3030</v>
+        <v>3003</v>
       </c>
       <c r="B1932" t="s">
-        <v>3028</v>
+        <v>2970</v>
       </c>
       <c r="C1932" t="s">
-        <v>225</v>
+        <v>1619</v>
       </c>
       <c r="D1932" t="s">
         <v>8</v>
       </c>
       <c r="E1932" t="s">
-        <v>3031</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1933">
       <c r="A1933" t="s">
-        <v>3032</v>
+        <v>3003</v>
       </c>
       <c r="B1933" t="s">
-        <v>368</v>
+        <v>2970</v>
       </c>
       <c r="C1933" t="s">
-        <v>3033</v>
+        <v>1624</v>
       </c>
       <c r="D1933" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1933" t="s">
-        <v>3034</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1934">
       <c r="A1934" t="s">
-        <v>3035</v>
+        <v>3003</v>
       </c>
       <c r="B1934" t="s">
-        <v>443</v>
+        <v>2970</v>
       </c>
       <c r="C1934" t="s">
-        <v>3036</v>
+        <v>1631</v>
       </c>
       <c r="D1934" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1934" t="s">
-        <v>3037</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1935">
       <c r="A1935" t="s">
-        <v>3038</v>
+        <v>3003</v>
       </c>
       <c r="B1935" t="s">
-        <v>444</v>
+        <v>2970</v>
       </c>
       <c r="C1935" t="s">
-        <v>3039</v>
+        <v>1598</v>
       </c>
       <c r="D1935" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1935" t="s">
-        <v>3040</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1936">
       <c r="A1936" t="s">
-        <v>3041</v>
+        <v>3003</v>
       </c>
       <c r="B1936" t="s">
-        <v>445</v>
+        <v>2970</v>
       </c>
       <c r="C1936" t="s">
-        <v>3042</v>
+        <v>1632</v>
       </c>
       <c r="D1936" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1936" t="s">
-        <v>3043</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1937">
       <c r="A1937" t="s">
-        <v>3044</v>
+        <v>3027</v>
       </c>
       <c r="B1937" t="s">
-        <v>3042</v>
+        <v>1287</v>
       </c>
       <c r="C1937" t="s">
-        <v>875</v>
+        <v>3028</v>
       </c>
       <c r="D1937" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1937" t="s">
-        <v>3045</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="1938">
       <c r="A1938" t="s">
-        <v>3044</v>
+        <v>3030</v>
       </c>
       <c r="B1938" t="s">
-        <v>3042</v>
+        <v>3028</v>
       </c>
       <c r="C1938" t="s">
-        <v>677</v>
+        <v>225</v>
       </c>
       <c r="D1938" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1938" t="s">
-        <v>3046</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="1939">
       <c r="A1939" t="s">
-        <v>3044</v>
+        <v>3032</v>
       </c>
       <c r="B1939" t="s">
-        <v>3042</v>
+        <v>368</v>
       </c>
       <c r="C1939" t="s">
-        <v>1467</v>
+        <v>3033</v>
       </c>
       <c r="D1939" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1939" t="s">
-        <v>3045</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="1940">
       <c r="A1940" t="s">
-        <v>3047</v>
+        <v>3035</v>
       </c>
       <c r="B1940" t="s">
-        <v>369</v>
+        <v>443</v>
       </c>
       <c r="C1940" t="s">
-        <v>3048</v>
+        <v>3036</v>
       </c>
       <c r="D1940" t="s">
         <v>13</v>
       </c>
       <c r="E1940" t="s">
-        <v>3049</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="1941">
       <c r="A1941" t="s">
-        <v>3050</v>
+        <v>3038</v>
       </c>
       <c r="B1941" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C1941" t="s">
-        <v>3051</v>
+        <v>3039</v>
       </c>
       <c r="D1941" t="s">
         <v>13</v>
       </c>
       <c r="E1941" t="s">
-        <v>3052</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="1942">
       <c r="A1942" t="s">
-        <v>3053</v>
+        <v>3041</v>
       </c>
       <c r="B1942" t="s">
-        <v>697</v>
+        <v>445</v>
       </c>
       <c r="C1942" t="s">
-        <v>3054</v>
+        <v>3042</v>
       </c>
       <c r="D1942" t="s">
         <v>13</v>
       </c>
       <c r="E1942" t="s">
-        <v>3055</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="1943">
       <c r="A1943" t="s">
-        <v>3056</v>
+        <v>3044</v>
       </c>
       <c r="B1943" t="s">
-        <v>447</v>
+        <v>3042</v>
       </c>
       <c r="C1943" t="s">
-        <v>3057</v>
+        <v>875</v>
       </c>
       <c r="D1943" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1943" t="s">
-        <v>3058</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="1944">
       <c r="A1944" t="s">
-        <v>3059</v>
+        <v>3044</v>
       </c>
       <c r="B1944" t="s">
-        <v>3026</v>
+        <v>3042</v>
       </c>
       <c r="C1944" t="s">
-        <v>3060</v>
+        <v>677</v>
       </c>
       <c r="D1944" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E1944" t="s">
-        <v>3061</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="1945">
       <c r="A1945" t="s">
-        <v>3062</v>
+        <v>3044</v>
       </c>
       <c r="B1945" t="s">
-        <v>719</v>
+        <v>3042</v>
       </c>
       <c r="C1945" t="s">
-        <v>476</v>
+        <v>1467</v>
       </c>
       <c r="D1945" t="s">
         <v>8</v>
       </c>
       <c r="E1945" t="s">
-        <v>3063</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="1946">
       <c r="A1946" t="s">
-        <v>3062</v>
+        <v>3047</v>
       </c>
       <c r="B1946" t="s">
-        <v>719</v>
+        <v>369</v>
       </c>
       <c r="C1946" t="s">
-        <v>2969</v>
+        <v>3048</v>
       </c>
       <c r="D1946" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1946" t="s">
-        <v>3063</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="1947">
       <c r="A1947" t="s">
-        <v>3062</v>
+        <v>3050</v>
       </c>
       <c r="B1947" t="s">
-        <v>719</v>
+        <v>446</v>
       </c>
       <c r="C1947" t="s">
-        <v>478</v>
+        <v>3051</v>
       </c>
       <c r="D1947" t="s">
         <v>13</v>
       </c>
       <c r="E1947" t="s">
-        <v>3063</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="1948">
       <c r="A1948" t="s">
-        <v>3064</v>
+        <v>3053</v>
       </c>
       <c r="B1948" t="s">
-        <v>3065</v>
+        <v>697</v>
       </c>
       <c r="C1948" t="s">
-        <v>347</v>
+        <v>3054</v>
       </c>
       <c r="D1948" t="s">
         <v>13</v>
       </c>
       <c r="E1948" t="s">
-        <v>3066</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="1949">
       <c r="A1949" t="s">
-        <v>3067</v>
+        <v>3056</v>
       </c>
       <c r="B1949" t="s">
-        <v>64</v>
+        <v>447</v>
       </c>
       <c r="C1949" t="s">
-        <v>405</v>
+        <v>3057</v>
       </c>
       <c r="D1949" t="s">
         <v>13</v>
       </c>
       <c r="E1949" t="s">
-        <v>3068</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="1950">
       <c r="A1950" t="s">
-        <v>3069</v>
+        <v>3059</v>
       </c>
       <c r="B1950" t="s">
-        <v>866</v>
+        <v>3026</v>
       </c>
       <c r="C1950" t="s">
-        <v>681</v>
+        <v>3060</v>
       </c>
       <c r="D1950" t="s">
         <v>13</v>
       </c>
       <c r="E1950" t="s">
-        <v>3070</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="1951">
       <c r="A1951" t="s">
-        <v>3069</v>
+        <v>3062</v>
       </c>
       <c r="B1951" t="s">
-        <v>866</v>
+        <v>719</v>
       </c>
       <c r="C1951" t="s">
-        <v>35</v>
+        <v>476</v>
       </c>
       <c r="D1951" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1951" t="s">
-        <v>3071</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="1952">
       <c r="A1952" t="s">
-        <v>3072</v>
+        <v>3062</v>
       </c>
       <c r="B1952" t="s">
-        <v>647</v>
+        <v>719</v>
       </c>
       <c r="C1952" t="s">
-        <v>1144</v>
+        <v>2969</v>
       </c>
       <c r="D1952" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1952" t="s">
-        <v>3073</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="1953">
       <c r="A1953" t="s">
-        <v>3074</v>
+        <v>3062</v>
       </c>
       <c r="B1953" t="s">
-        <v>1216</v>
+        <v>719</v>
       </c>
       <c r="C1953" t="s">
-        <v>1144</v>
+        <v>478</v>
       </c>
       <c r="D1953" t="s">
         <v>13</v>
       </c>
       <c r="E1953" t="s">
-        <v>3075</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="1954">
       <c r="A1954" t="s">
-        <v>3076</v>
+        <v>3064</v>
       </c>
       <c r="B1954" t="s">
-        <v>1316</v>
+        <v>3065</v>
       </c>
       <c r="C1954" t="s">
-        <v>1144</v>
+        <v>347</v>
       </c>
       <c r="D1954" t="s">
         <v>13</v>
       </c>
       <c r="E1954" t="s">
-        <v>3077</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="1955">
       <c r="A1955" t="s">
-        <v>3078</v>
+        <v>3067</v>
       </c>
       <c r="B1955" t="s">
-        <v>175</v>
+        <v>64</v>
       </c>
       <c r="C1955" t="s">
-        <v>1424</v>
+        <v>405</v>
       </c>
       <c r="D1955" t="s">
         <v>13</v>
       </c>
       <c r="E1955" t="s">
-        <v>3079</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="1956">
       <c r="A1956" t="s">
-        <v>3080</v>
+        <v>3069</v>
       </c>
       <c r="B1956" t="s">
-        <v>175</v>
+        <v>866</v>
       </c>
       <c r="C1956" t="s">
-        <v>1424</v>
+        <v>681</v>
       </c>
       <c r="D1956" t="s">
         <v>13</v>
       </c>
       <c r="E1956" t="s">
-        <v>3081</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="1957">
       <c r="A1957" t="s">
-        <v>3082</v>
+        <v>3069</v>
       </c>
       <c r="B1957" t="s">
-        <v>3083</v>
+        <v>866</v>
       </c>
       <c r="C1957" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="D1957" t="s">
         <v>13</v>
       </c>
       <c r="E1957" t="s">
-        <v>3084</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="1958">
       <c r="A1958" t="s">
-        <v>3085</v>
+        <v>3072</v>
       </c>
       <c r="B1958" t="s">
-        <v>3086</v>
+        <v>647</v>
       </c>
       <c r="C1958" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="D1958" t="s">
         <v>13</v>
       </c>
       <c r="E1958" t="s">
-        <v>3087</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="1959">
       <c r="A1959" t="s">
-        <v>3088</v>
+        <v>3074</v>
       </c>
       <c r="B1959" t="s">
-        <v>798</v>
+        <v>1216</v>
       </c>
       <c r="C1959" t="s">
-        <v>3089</v>
+        <v>1144</v>
       </c>
       <c r="D1959" t="s">
         <v>13</v>
       </c>
       <c r="E1959" t="s">
-        <v>3090</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="1960">
       <c r="A1960" t="s">
-        <v>3091</v>
+        <v>3076</v>
       </c>
       <c r="B1960" t="s">
-        <v>269</v>
+        <v>1316</v>
       </c>
       <c r="C1960" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="D1960" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1960" t="s">
-        <v>3092</v>
+        <v>3077</v>
       </c>
     </row>
     <row r="1961">
       <c r="A1961" t="s">
-        <v>3091</v>
+        <v>3078</v>
       </c>
       <c r="B1961" t="s">
-        <v>269</v>
+        <v>175</v>
       </c>
       <c r="C1961" t="s">
-        <v>2037</v>
+        <v>1424</v>
       </c>
       <c r="D1961" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1961" t="s">
-        <v>3092</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="1962">
       <c r="A1962" t="s">
-        <v>3093</v>
+        <v>3080</v>
       </c>
       <c r="B1962" t="s">
-        <v>2037</v>
+        <v>175</v>
       </c>
       <c r="C1962" t="s">
-        <v>3094</v>
+        <v>1424</v>
       </c>
       <c r="D1962" t="s">
         <v>13</v>
       </c>
       <c r="E1962" t="s">
-        <v>3095</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="1963">
       <c r="A1963" t="s">
-        <v>3096</v>
+        <v>3082</v>
       </c>
       <c r="B1963" t="s">
-        <v>3097</v>
+        <v>3083</v>
       </c>
       <c r="C1963" t="s">
-        <v>706</v>
+        <v>121</v>
       </c>
       <c r="D1963" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E1963" t="s">
-        <v>3098</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="1964">
       <c r="A1964" t="s">
-        <v>3099</v>
+        <v>3085</v>
       </c>
       <c r="B1964" t="s">
-        <v>2371</v>
+        <v>3086</v>
       </c>
       <c r="C1964" t="s">
-        <v>3100</v>
+        <v>1146</v>
       </c>
       <c r="D1964" t="s">
         <v>13</v>
       </c>
       <c r="E1964" t="s">
-        <v>3101</v>
+        <v>3087</v>
       </c>
     </row>
     <row r="1965">
       <c r="A1965" t="s">
-        <v>3102</v>
+        <v>3088</v>
       </c>
       <c r="B1965" t="s">
-        <v>2423</v>
+        <v>798</v>
       </c>
       <c r="C1965" t="s">
-        <v>3103</v>
+        <v>3089</v>
       </c>
       <c r="D1965" t="s">
         <v>13</v>
       </c>
       <c r="E1965" t="s">
-        <v>3104</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="1966">
       <c r="A1966" t="s">
-        <v>1946</v>
+        <v>3091</v>
       </c>
       <c r="B1966" t="s">
-        <v>1946</v>
+        <v>269</v>
       </c>
       <c r="C1966" t="s">
-        <v>648</v>
+        <v>1146</v>
       </c>
       <c r="D1966" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1966" t="s">
-        <v>3105</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="1967">
       <c r="A1967" t="s">
-        <v>3106</v>
+        <v>3091</v>
       </c>
       <c r="B1967" t="s">
-        <v>3103</v>
+        <v>269</v>
       </c>
       <c r="C1967" t="s">
-        <v>648</v>
+        <v>2037</v>
       </c>
       <c r="D1967" t="s">
         <v>8</v>
       </c>
       <c r="E1967" t="s">
-        <v>2422</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="1968">
       <c r="A1968" t="s">
-        <v>3106</v>
+        <v>3093</v>
       </c>
       <c r="B1968" t="s">
-        <v>3103</v>
+        <v>2037</v>
       </c>
       <c r="C1968" t="s">
-        <v>3107</v>
+        <v>3094</v>
       </c>
       <c r="D1968" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1968" t="s">
-        <v>2422</v>
+        <v>3095</v>
       </c>
     </row>
     <row r="1969">
       <c r="A1969" t="s">
-        <v>3108</v>
+        <v>3096</v>
       </c>
       <c r="B1969" t="s">
-        <v>3107</v>
+        <v>3097</v>
       </c>
       <c r="C1969" t="s">
-        <v>3109</v>
+        <v>706</v>
       </c>
       <c r="D1969" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E1969" t="s">
-        <v>3110</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="1970">
       <c r="A1970" t="s">
-        <v>2078</v>
+        <v>3099</v>
       </c>
       <c r="B1970" t="s">
-        <v>2078</v>
+        <v>2371</v>
       </c>
       <c r="C1970" t="s">
-        <v>648</v>
+        <v>3100</v>
       </c>
       <c r="D1970" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E1970" t="s">
-        <v>3111</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="1971">
       <c r="A1971" t="s">
-        <v>3112</v>
+        <v>3102</v>
       </c>
       <c r="B1971" t="s">
-        <v>222</v>
+        <v>2423</v>
       </c>
       <c r="C1971" t="s">
-        <v>2078</v>
+        <v>3103</v>
       </c>
       <c r="D1971" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1971" t="s">
-        <v>3113</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="1972">
       <c r="A1972" t="s">
-        <v>3114</v>
+        <v>1946</v>
       </c>
       <c r="B1972" t="s">
-        <v>3094</v>
+        <v>1946</v>
       </c>
       <c r="C1972" t="s">
-        <v>1942</v>
+        <v>648</v>
       </c>
       <c r="D1972" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E1972" t="s">
-        <v>3115</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="1973">
       <c r="A1973" t="s">
-        <v>3114</v>
+        <v>3106</v>
       </c>
       <c r="B1973" t="s">
-        <v>3094</v>
+        <v>3103</v>
       </c>
       <c r="C1973" t="s">
-        <v>706</v>
+        <v>648</v>
       </c>
       <c r="D1973" t="s">
         <v>8</v>
       </c>
       <c r="E1973" t="s">
-        <v>3116</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="1974">
       <c r="A1974" t="s">
-        <v>3114</v>
+        <v>3106</v>
       </c>
       <c r="B1974" t="s">
-        <v>3094</v>
+        <v>3103</v>
       </c>
       <c r="C1974" t="s">
-        <v>3117</v>
+        <v>3107</v>
       </c>
       <c r="D1974" t="s">
         <v>8</v>
       </c>
       <c r="E1974" t="s">
-        <v>3115</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="1975">
       <c r="A1975" t="s">
-        <v>3114</v>
+        <v>3108</v>
       </c>
       <c r="B1975" t="s">
-        <v>3094</v>
+        <v>3107</v>
       </c>
       <c r="C1975" t="s">
-        <v>796</v>
+        <v>3109</v>
       </c>
       <c r="D1975" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1975" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
     </row>
     <row r="1976">
       <c r="A1976" t="s">
-        <v>3114</v>
+        <v>2078</v>
       </c>
       <c r="B1976" t="s">
-        <v>3094</v>
+        <v>2078</v>
       </c>
       <c r="C1976" t="s">
-        <v>2369</v>
+        <v>648</v>
       </c>
       <c r="D1976" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E1976" t="s">
-        <v>3118</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="1977">
       <c r="A1977" t="s">
-        <v>3114</v>
+        <v>3112</v>
       </c>
       <c r="B1977" t="s">
-        <v>3094</v>
+        <v>222</v>
       </c>
       <c r="C1977" t="s">
-        <v>2665</v>
+        <v>2078</v>
       </c>
       <c r="D1977" t="s">
         <v>8</v>
       </c>
       <c r="E1977" t="s">
-        <v>3119</v>
+        <v>3113</v>
       </c>
     </row>
     <row r="1978">
@@ -46230,13 +46230,13 @@
         <v>3094</v>
       </c>
       <c r="C1978" t="s">
-        <v>798</v>
+        <v>1942</v>
       </c>
       <c r="D1978" t="s">
         <v>8</v>
       </c>
       <c r="E1978" t="s">
-        <v>3118</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="1979">
@@ -46247,13 +46247,13 @@
         <v>3094</v>
       </c>
       <c r="C1979" t="s">
-        <v>2371</v>
+        <v>706</v>
       </c>
       <c r="D1979" t="s">
         <v>8</v>
       </c>
       <c r="E1979" t="s">
-        <v>3118</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="1980">
@@ -46264,7 +46264,7 @@
         <v>3094</v>
       </c>
       <c r="C1980" t="s">
-        <v>2423</v>
+        <v>3117</v>
       </c>
       <c r="D1980" t="s">
         <v>8</v>
@@ -46281,13 +46281,13 @@
         <v>3094</v>
       </c>
       <c r="C1981" t="s">
-        <v>3120</v>
+        <v>796</v>
       </c>
       <c r="D1981" t="s">
         <v>8</v>
       </c>
       <c r="E1981" t="s">
-        <v>3116</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="1982">
@@ -46298,13 +46298,13 @@
         <v>3094</v>
       </c>
       <c r="C1982" t="s">
-        <v>2667</v>
+        <v>2369</v>
       </c>
       <c r="D1982" t="s">
         <v>8</v>
       </c>
       <c r="E1982" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="1983">
@@ -46315,183 +46315,183 @@
         <v>3094</v>
       </c>
       <c r="C1983" t="s">
-        <v>3121</v>
+        <v>2665</v>
       </c>
       <c r="D1983" t="s">
         <v>8</v>
       </c>
       <c r="E1983" t="s">
-        <v>3115</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="1984">
       <c r="A1984" t="s">
-        <v>3122</v>
+        <v>3114</v>
       </c>
       <c r="B1984" t="s">
-        <v>1174</v>
+        <v>3094</v>
       </c>
       <c r="C1984" t="s">
-        <v>3123</v>
+        <v>798</v>
       </c>
       <c r="D1984" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1984" t="s">
-        <v>3124</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="1985">
       <c r="A1985" t="s">
-        <v>3125</v>
+        <v>3114</v>
       </c>
       <c r="B1985" t="s">
-        <v>269</v>
+        <v>3094</v>
       </c>
       <c r="C1985" t="s">
-        <v>706</v>
+        <v>2371</v>
       </c>
       <c r="D1985" t="s">
         <v>8</v>
       </c>
       <c r="E1985" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="1986">
       <c r="A1986" t="s">
-        <v>3125</v>
+        <v>3114</v>
       </c>
       <c r="B1986" t="s">
-        <v>269</v>
+        <v>3094</v>
       </c>
       <c r="C1986" t="s">
-        <v>3120</v>
+        <v>2423</v>
       </c>
       <c r="D1986" t="s">
         <v>8</v>
       </c>
       <c r="E1986" t="s">
-        <v>3126</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="1987">
       <c r="A1987" t="s">
-        <v>3127</v>
+        <v>3114</v>
       </c>
       <c r="B1987" t="s">
+        <v>3094</v>
+      </c>
+      <c r="C1987" t="s">
         <v>3120</v>
       </c>
-      <c r="C1987" t="s">
-        <v>3128</v>
-      </c>
       <c r="D1987" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1987" t="s">
-        <v>3129</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="1988">
       <c r="A1988" t="s">
-        <v>3130</v>
+        <v>3114</v>
       </c>
       <c r="B1988" t="s">
-        <v>3128</v>
+        <v>3094</v>
       </c>
       <c r="C1988" t="s">
-        <v>648</v>
+        <v>2667</v>
       </c>
       <c r="D1988" t="s">
         <v>8</v>
       </c>
       <c r="E1988" t="s">
-        <v>3131</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="1989">
       <c r="A1989" t="s">
-        <v>3130</v>
+        <v>3114</v>
       </c>
       <c r="B1989" t="s">
-        <v>3128</v>
+        <v>3094</v>
       </c>
       <c r="C1989" t="s">
-        <v>2654</v>
+        <v>3121</v>
       </c>
       <c r="D1989" t="s">
         <v>8</v>
       </c>
       <c r="E1989" t="s">
-        <v>3131</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="1990">
       <c r="A1990" t="s">
-        <v>3130</v>
+        <v>3122</v>
       </c>
       <c r="B1990" t="s">
-        <v>3128</v>
+        <v>1174</v>
       </c>
       <c r="C1990" t="s">
-        <v>1157</v>
+        <v>3123</v>
       </c>
       <c r="D1990" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1990" t="s">
-        <v>3131</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="1991">
       <c r="A1991" t="s">
-        <v>3130</v>
+        <v>3125</v>
       </c>
       <c r="B1991" t="s">
-        <v>3128</v>
+        <v>269</v>
       </c>
       <c r="C1991" t="s">
-        <v>2829</v>
+        <v>706</v>
       </c>
       <c r="D1991" t="s">
         <v>8</v>
       </c>
       <c r="E1991" t="s">
-        <v>3132</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="1992">
       <c r="A1992" t="s">
-        <v>3130</v>
+        <v>3125</v>
       </c>
       <c r="B1992" t="s">
-        <v>3128</v>
+        <v>269</v>
       </c>
       <c r="C1992" t="s">
-        <v>3107</v>
+        <v>3120</v>
       </c>
       <c r="D1992" t="s">
         <v>8</v>
       </c>
       <c r="E1992" t="s">
-        <v>3131</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="1993">
       <c r="A1993" t="s">
-        <v>3130</v>
+        <v>3127</v>
       </c>
       <c r="B1993" t="s">
+        <v>3120</v>
+      </c>
+      <c r="C1993" t="s">
         <v>3128</v>
       </c>
-      <c r="C1993" t="s">
-        <v>1174</v>
-      </c>
       <c r="D1993" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1993" t="s">
-        <v>3131</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="1994">
@@ -46502,13 +46502,13 @@
         <v>3128</v>
       </c>
       <c r="C1994" t="s">
-        <v>2833</v>
+        <v>648</v>
       </c>
       <c r="D1994" t="s">
         <v>8</v>
       </c>
       <c r="E1994" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="1995">
@@ -46519,7 +46519,7 @@
         <v>3128</v>
       </c>
       <c r="C1995" t="s">
-        <v>3133</v>
+        <v>2654</v>
       </c>
       <c r="D1995" t="s">
         <v>8</v>
@@ -46530,95 +46530,95 @@
     </row>
     <row r="1996">
       <c r="A1996" t="s">
-        <v>3134</v>
+        <v>3130</v>
       </c>
       <c r="B1996" t="s">
-        <v>2833</v>
+        <v>3128</v>
       </c>
       <c r="C1996" t="s">
-        <v>3135</v>
+        <v>1157</v>
       </c>
       <c r="D1996" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1996" t="s">
-        <v>3136</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="1997">
       <c r="A1997" t="s">
-        <v>3137</v>
+        <v>3130</v>
       </c>
       <c r="B1997" t="s">
-        <v>2667</v>
+        <v>3128</v>
       </c>
       <c r="C1997" t="s">
-        <v>3138</v>
+        <v>2829</v>
       </c>
       <c r="D1997" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1997" t="s">
-        <v>3139</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="1998">
       <c r="A1998" t="s">
-        <v>3140</v>
+        <v>3130</v>
       </c>
       <c r="B1998" t="s">
-        <v>3121</v>
+        <v>3128</v>
       </c>
       <c r="C1998" t="s">
-        <v>3141</v>
+        <v>3107</v>
       </c>
       <c r="D1998" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1998" t="s">
-        <v>3142</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="1999">
       <c r="A1999" t="s">
-        <v>3143</v>
+        <v>3130</v>
       </c>
       <c r="B1999" t="s">
-        <v>3141</v>
+        <v>3128</v>
       </c>
       <c r="C1999" t="s">
-        <v>1942</v>
+        <v>1174</v>
       </c>
       <c r="D1999" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1999" t="s">
-        <v>3144</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="2000">
       <c r="A2000" t="s">
-        <v>3143</v>
+        <v>3130</v>
       </c>
       <c r="B2000" t="s">
-        <v>3141</v>
+        <v>3128</v>
       </c>
       <c r="C2000" t="s">
-        <v>2654</v>
+        <v>2833</v>
       </c>
       <c r="D2000" t="s">
         <v>8</v>
       </c>
       <c r="E2000" t="s">
-        <v>3144</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="2001">
       <c r="A2001" t="s">
-        <v>3143</v>
+        <v>3130</v>
       </c>
       <c r="B2001" t="s">
-        <v>3141</v>
+        <v>3128</v>
       </c>
       <c r="C2001" t="s">
         <v>3133</v>
@@ -46627,1468 +46627,1570 @@
         <v>8</v>
       </c>
       <c r="E2001" t="s">
-        <v>3144</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="2002">
       <c r="A2002" t="s">
-        <v>3145</v>
+        <v>3134</v>
       </c>
       <c r="B2002" t="s">
-        <v>1175</v>
+        <v>2833</v>
       </c>
       <c r="C2002" t="s">
-        <v>3146</v>
+        <v>3135</v>
       </c>
       <c r="D2002" t="s">
         <v>13</v>
       </c>
       <c r="E2002" t="s">
-        <v>3147</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="2003">
       <c r="A2003" t="s">
-        <v>3148</v>
+        <v>3137</v>
       </c>
       <c r="B2003" t="s">
-        <v>3133</v>
+        <v>2667</v>
       </c>
       <c r="C2003" t="s">
-        <v>3149</v>
+        <v>3138</v>
       </c>
       <c r="D2003" t="s">
         <v>13</v>
       </c>
       <c r="E2003" t="s">
-        <v>3150</v>
+        <v>3139</v>
       </c>
     </row>
     <row r="2004">
       <c r="A2004" t="s">
-        <v>3151</v>
+        <v>3140</v>
       </c>
       <c r="B2004" t="s">
-        <v>3149</v>
+        <v>3121</v>
       </c>
       <c r="C2004" t="s">
-        <v>1159</v>
+        <v>3141</v>
       </c>
       <c r="D2004" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2004" t="s">
-        <v>3152</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="2005">
       <c r="A2005" t="s">
-        <v>3151</v>
+        <v>3143</v>
       </c>
       <c r="B2005" t="s">
-        <v>3149</v>
+        <v>3141</v>
       </c>
       <c r="C2005" t="s">
-        <v>2831</v>
+        <v>1942</v>
       </c>
       <c r="D2005" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2005" t="s">
-        <v>3152</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="2006">
       <c r="A2006" t="s">
-        <v>3151</v>
+        <v>3143</v>
       </c>
       <c r="B2006" t="s">
-        <v>3149</v>
+        <v>3141</v>
       </c>
       <c r="C2006" t="s">
-        <v>1175</v>
+        <v>2654</v>
       </c>
       <c r="D2006" t="s">
         <v>8</v>
       </c>
       <c r="E2006" t="s">
-        <v>3152</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="2007">
       <c r="A2007" t="s">
-        <v>3151</v>
+        <v>3143</v>
       </c>
       <c r="B2007" t="s">
-        <v>3149</v>
+        <v>3141</v>
       </c>
       <c r="C2007" t="s">
-        <v>2834</v>
+        <v>3133</v>
       </c>
       <c r="D2007" t="s">
         <v>8</v>
       </c>
       <c r="E2007" t="s">
-        <v>3152</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="2008">
       <c r="A2008" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B2008" t="s">
-        <v>2834</v>
+        <v>1175</v>
       </c>
       <c r="C2008" t="s">
-        <v>3154</v>
+        <v>3146</v>
       </c>
       <c r="D2008" t="s">
         <v>13</v>
       </c>
       <c r="E2008" t="s">
-        <v>3155</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="2009">
       <c r="A2009" t="s">
-        <v>3156</v>
+        <v>3148</v>
       </c>
       <c r="B2009" t="s">
-        <v>3156</v>
+        <v>3133</v>
       </c>
       <c r="C2009" t="s">
-        <v>3117</v>
+        <v>3149</v>
       </c>
       <c r="D2009" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2009" t="s">
-        <v>3157</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="2010">
       <c r="A2010" t="s">
-        <v>3156</v>
+        <v>3151</v>
       </c>
       <c r="B2010" t="s">
-        <v>3156</v>
+        <v>3149</v>
       </c>
       <c r="C2010" t="s">
-        <v>3121</v>
+        <v>1159</v>
       </c>
       <c r="D2010" t="s">
         <v>8</v>
       </c>
       <c r="E2010" t="s">
-        <v>3157</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="2011">
       <c r="A2011" t="s">
-        <v>3158</v>
+        <v>3151</v>
       </c>
       <c r="B2011" t="s">
-        <v>3158</v>
+        <v>3149</v>
       </c>
       <c r="C2011" t="s">
-        <v>1146</v>
+        <v>2831</v>
       </c>
       <c r="D2011" t="s">
         <v>8</v>
       </c>
       <c r="E2011" t="s">
-        <v>3159</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="2012">
       <c r="A2012" t="s">
-        <v>3160</v>
+        <v>3151</v>
       </c>
       <c r="B2012" t="s">
-        <v>3160</v>
+        <v>3149</v>
       </c>
       <c r="C2012" t="s">
-        <v>2499</v>
+        <v>1175</v>
       </c>
       <c r="D2012" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2012" t="s">
-        <v>3161</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="2013">
       <c r="A2013" t="s">
-        <v>3162</v>
+        <v>3151</v>
       </c>
       <c r="B2013" t="s">
-        <v>1820</v>
+        <v>3149</v>
       </c>
       <c r="C2013" t="s">
-        <v>1202</v>
+        <v>2834</v>
       </c>
       <c r="D2013" t="s">
         <v>8</v>
       </c>
       <c r="E2013" t="s">
-        <v>3163</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="2014">
       <c r="A2014" t="s">
-        <v>3162</v>
+        <v>3153</v>
       </c>
       <c r="B2014" t="s">
-        <v>1820</v>
+        <v>2834</v>
       </c>
       <c r="C2014" t="s">
-        <v>1806</v>
+        <v>3154</v>
       </c>
       <c r="D2014" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2014" t="s">
-        <v>3163</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="2015">
       <c r="A2015" t="s">
-        <v>3164</v>
+        <v>3156</v>
       </c>
       <c r="B2015" t="s">
-        <v>64</v>
+        <v>3156</v>
       </c>
       <c r="C2015" t="s">
-        <v>421</v>
+        <v>3117</v>
       </c>
       <c r="D2015" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2015" t="s">
-        <v>3165</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="2016">
       <c r="A2016" t="s">
-        <v>3164</v>
+        <v>3156</v>
       </c>
       <c r="B2016" t="s">
-        <v>64</v>
+        <v>3156</v>
       </c>
       <c r="C2016" t="s">
-        <v>354</v>
+        <v>3121</v>
       </c>
       <c r="D2016" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2016" t="s">
-        <v>3166</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="2017">
       <c r="A2017" t="s">
-        <v>3167</v>
+        <v>3158</v>
       </c>
       <c r="B2017" t="s">
-        <v>3168</v>
+        <v>3158</v>
       </c>
       <c r="C2017" t="s">
-        <v>33</v>
+        <v>1146</v>
       </c>
       <c r="D2017" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2017" t="s">
-        <v>3169</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="2018">
       <c r="A2018" t="s">
-        <v>3170</v>
+        <v>3160</v>
       </c>
       <c r="B2018" t="s">
-        <v>3171</v>
+        <v>3160</v>
       </c>
       <c r="C2018" t="s">
-        <v>33</v>
+        <v>2499</v>
       </c>
       <c r="D2018" t="s">
         <v>13</v>
       </c>
       <c r="E2018" t="s">
-        <v>3172</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="2019">
       <c r="A2019" t="s">
-        <v>3173</v>
+        <v>3162</v>
       </c>
       <c r="B2019" t="s">
-        <v>3174</v>
+        <v>1820</v>
       </c>
       <c r="C2019" t="s">
-        <v>505</v>
+        <v>1202</v>
       </c>
       <c r="D2019" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2019" t="s">
-        <v>3175</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="2020">
       <c r="A2020" t="s">
-        <v>1021</v>
+        <v>3162</v>
       </c>
       <c r="B2020" t="s">
-        <v>1021</v>
+        <v>1820</v>
       </c>
       <c r="C2020" t="s">
-        <v>113</v>
+        <v>1806</v>
       </c>
       <c r="D2020" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E2020" t="s">
-        <v>3176</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="2021">
       <c r="A2021" t="s">
-        <v>1021</v>
+        <v>3164</v>
       </c>
       <c r="B2021" t="s">
-        <v>1021</v>
+        <v>64</v>
       </c>
       <c r="C2021" t="s">
-        <v>117</v>
+        <v>421</v>
       </c>
       <c r="D2021" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2021" t="s">
-        <v>3176</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="2022">
       <c r="A2022" t="s">
-        <v>1021</v>
+        <v>3164</v>
       </c>
       <c r="B2022" t="s">
-        <v>1021</v>
+        <v>64</v>
       </c>
       <c r="C2022" t="s">
-        <v>119</v>
+        <v>354</v>
       </c>
       <c r="D2022" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2022" t="s">
-        <v>3177</v>
+        <v>3166</v>
       </c>
     </row>
     <row r="2023">
       <c r="A2023" t="s">
-        <v>1021</v>
+        <v>3167</v>
       </c>
       <c r="B2023" t="s">
-        <v>1021</v>
+        <v>3168</v>
       </c>
       <c r="C2023" t="s">
-        <v>121</v>
+        <v>33</v>
       </c>
       <c r="D2023" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2023" t="s">
-        <v>3176</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="2024">
       <c r="A2024" t="s">
-        <v>1021</v>
+        <v>3170</v>
       </c>
       <c r="B2024" t="s">
-        <v>1021</v>
+        <v>3171</v>
       </c>
       <c r="C2024" t="s">
-        <v>481</v>
+        <v>33</v>
       </c>
       <c r="D2024" t="s">
         <v>13</v>
       </c>
       <c r="E2024" t="s">
-        <v>3176</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="2025">
       <c r="A2025" t="s">
-        <v>3178</v>
+        <v>3173</v>
       </c>
       <c r="B2025" t="s">
-        <v>3178</v>
+        <v>3174</v>
       </c>
       <c r="C2025" t="s">
-        <v>1698</v>
+        <v>505</v>
       </c>
       <c r="D2025" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2025" t="s">
-        <v>3179</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="2026">
       <c r="A2026" t="s">
-        <v>3178</v>
+        <v>1021</v>
       </c>
       <c r="B2026" t="s">
-        <v>3178</v>
+        <v>1021</v>
       </c>
       <c r="C2026" t="s">
-        <v>1021</v>
+        <v>113</v>
       </c>
       <c r="D2026" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E2026" t="s">
-        <v>3179</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="2027">
       <c r="A2027" t="s">
-        <v>3180</v>
+        <v>1021</v>
       </c>
       <c r="B2027" t="s">
-        <v>3181</v>
+        <v>1021</v>
       </c>
       <c r="C2027" t="s">
-        <v>1021</v>
+        <v>117</v>
       </c>
       <c r="D2027" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E2027" t="s">
-        <v>1702</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="2028">
       <c r="A2028" t="s">
-        <v>3182</v>
+        <v>1021</v>
       </c>
       <c r="B2028" t="s">
-        <v>3183</v>
+        <v>1021</v>
       </c>
       <c r="C2028" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="D2028" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E2028" t="s">
-        <v>3184</v>
+        <v>3177</v>
       </c>
     </row>
     <row r="2029">
       <c r="A2029" t="s">
-        <v>3182</v>
+        <v>1021</v>
       </c>
       <c r="B2029" t="s">
-        <v>3183</v>
+        <v>1021</v>
       </c>
       <c r="C2029" t="s">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="D2029" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E2029" t="s">
-        <v>3185</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="2030">
       <c r="A2030" t="s">
-        <v>3182</v>
+        <v>1021</v>
       </c>
       <c r="B2030" t="s">
-        <v>3183</v>
+        <v>1021</v>
       </c>
       <c r="C2030" t="s">
-        <v>2607</v>
+        <v>481</v>
       </c>
       <c r="D2030" t="s">
         <v>13</v>
       </c>
       <c r="E2030" t="s">
-        <v>3184</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="2031">
       <c r="A2031" t="s">
-        <v>3182</v>
+        <v>3178</v>
       </c>
       <c r="B2031" t="s">
-        <v>3183</v>
+        <v>3178</v>
       </c>
       <c r="C2031" t="s">
-        <v>1170</v>
+        <v>1698</v>
       </c>
       <c r="D2031" t="s">
         <v>8</v>
       </c>
       <c r="E2031" t="s">
-        <v>3185</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="2032">
       <c r="A2032" t="s">
-        <v>3182</v>
+        <v>3178</v>
       </c>
       <c r="B2032" t="s">
-        <v>3183</v>
+        <v>3178</v>
       </c>
       <c r="C2032" t="s">
-        <v>642</v>
+        <v>1021</v>
       </c>
       <c r="D2032" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2032" t="s">
-        <v>3186</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="2033">
       <c r="A2033" t="s">
-        <v>3187</v>
+        <v>3180</v>
       </c>
       <c r="B2033" t="s">
-        <v>64</v>
+        <v>3181</v>
       </c>
       <c r="C2033" t="s">
-        <v>172</v>
+        <v>1021</v>
       </c>
       <c r="D2033" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2033" t="s">
-        <v>3188</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="2034">
       <c r="A2034" t="s">
-        <v>3189</v>
+        <v>3182</v>
       </c>
       <c r="B2034" t="s">
-        <v>335</v>
+        <v>3183</v>
       </c>
       <c r="C2034" t="s">
-        <v>225</v>
+        <v>53</v>
       </c>
       <c r="D2034" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2034" t="s">
-        <v>3190</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="2035">
       <c r="A2035" t="s">
-        <v>3191</v>
+        <v>3182</v>
       </c>
       <c r="B2035" t="s">
-        <v>64</v>
+        <v>3183</v>
       </c>
       <c r="C2035" t="s">
-        <v>1021</v>
+        <v>16</v>
       </c>
       <c r="D2035" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2035" t="s">
-        <v>3192</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="2036">
       <c r="A2036" t="s">
-        <v>3193</v>
+        <v>3182</v>
       </c>
       <c r="B2036" t="s">
-        <v>3193</v>
+        <v>3183</v>
       </c>
       <c r="C2036" t="s">
-        <v>1946</v>
+        <v>2607</v>
       </c>
       <c r="D2036" t="s">
         <v>13</v>
       </c>
       <c r="E2036" t="s">
-        <v>3194</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="2037">
       <c r="A2037" t="s">
-        <v>3193</v>
+        <v>3182</v>
       </c>
       <c r="B2037" t="s">
-        <v>3193</v>
+        <v>3183</v>
       </c>
       <c r="C2037" t="s">
-        <v>2078</v>
+        <v>1170</v>
       </c>
       <c r="D2037" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2037" t="s">
-        <v>3195</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="2038">
       <c r="A2038" t="s">
-        <v>3196</v>
+        <v>3182</v>
       </c>
       <c r="B2038" t="s">
-        <v>3196</v>
+        <v>3183</v>
       </c>
       <c r="C2038" t="s">
-        <v>2081</v>
+        <v>642</v>
       </c>
       <c r="D2038" t="s">
         <v>13</v>
       </c>
       <c r="E2038" t="s">
-        <v>3197</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="2039">
       <c r="A2039" t="s">
-        <v>3198</v>
+        <v>3187</v>
       </c>
       <c r="B2039" t="s">
-        <v>1375</v>
+        <v>64</v>
       </c>
       <c r="C2039" t="s">
-        <v>285</v>
+        <v>172</v>
       </c>
       <c r="D2039" t="s">
         <v>13</v>
       </c>
       <c r="E2039" t="s">
-        <v>3199</v>
+        <v>3188</v>
       </c>
     </row>
     <row r="2040">
       <c r="A2040" t="s">
-        <v>3200</v>
+        <v>3189</v>
       </c>
       <c r="B2040" t="s">
-        <v>206</v>
+        <v>335</v>
       </c>
       <c r="C2040" t="s">
-        <v>347</v>
+        <v>225</v>
       </c>
       <c r="D2040" t="s">
         <v>13</v>
       </c>
       <c r="E2040" t="s">
-        <v>3201</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="2041">
       <c r="A2041" t="s">
-        <v>3202</v>
+        <v>3191</v>
       </c>
       <c r="B2041" t="s">
-        <v>1375</v>
+        <v>64</v>
       </c>
       <c r="C2041" t="s">
-        <v>103</v>
+        <v>1021</v>
       </c>
       <c r="D2041" t="s">
         <v>13</v>
       </c>
       <c r="E2041" t="s">
-        <v>3203</v>
+        <v>3192</v>
       </c>
     </row>
     <row r="2042">
       <c r="A2042" t="s">
-        <v>3204</v>
+        <v>3193</v>
       </c>
       <c r="B2042" t="s">
-        <v>1310</v>
+        <v>3193</v>
       </c>
       <c r="C2042" t="s">
-        <v>29</v>
+        <v>1946</v>
       </c>
       <c r="D2042" t="s">
         <v>13</v>
       </c>
       <c r="E2042" t="s">
-        <v>3205</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="2043">
       <c r="A2043" t="s">
-        <v>3206</v>
+        <v>3193</v>
       </c>
       <c r="B2043" t="s">
-        <v>3206</v>
+        <v>3193</v>
       </c>
       <c r="C2043" t="s">
-        <v>890</v>
+        <v>2078</v>
       </c>
       <c r="D2043" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2043" t="s">
-        <v>3207</v>
+        <v>3195</v>
       </c>
     </row>
     <row r="2044">
       <c r="A2044" t="s">
-        <v>3206</v>
+        <v>3196</v>
       </c>
       <c r="B2044" t="s">
-        <v>3208</v>
+        <v>3196</v>
       </c>
       <c r="C2044" t="s">
-        <v>373</v>
+        <v>2081</v>
       </c>
       <c r="D2044" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2044" t="s">
-        <v>732</v>
+        <v>3197</v>
       </c>
     </row>
     <row r="2045">
       <c r="A2045" t="s">
-        <v>3209</v>
+        <v>3198</v>
       </c>
       <c r="B2045" t="s">
-        <v>3210</v>
+        <v>1375</v>
       </c>
       <c r="C2045" t="s">
-        <v>3211</v>
+        <v>285</v>
       </c>
       <c r="D2045" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2045" t="s">
-        <v>3212</v>
+        <v>3199</v>
       </c>
     </row>
     <row r="2046">
       <c r="A2046" t="s">
-        <v>2265</v>
+        <v>3200</v>
       </c>
       <c r="B2046" t="s">
-        <v>2265</v>
+        <v>206</v>
       </c>
       <c r="C2046" t="s">
-        <v>3211</v>
+        <v>347</v>
       </c>
       <c r="D2046" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2046" t="s">
-        <v>3213</v>
+        <v>3201</v>
       </c>
     </row>
     <row r="2047">
       <c r="A2047" t="s">
-        <v>2265</v>
+        <v>3202</v>
       </c>
       <c r="B2047" t="s">
-        <v>3214</v>
+        <v>1375</v>
       </c>
       <c r="C2047" t="s">
-        <v>2265</v>
+        <v>103</v>
       </c>
       <c r="D2047" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2047" t="s">
-        <v>3215</v>
+        <v>3203</v>
       </c>
     </row>
     <row r="2048">
       <c r="A2048" t="s">
-        <v>3216</v>
+        <v>3204</v>
       </c>
       <c r="B2048" t="s">
-        <v>3217</v>
+        <v>1310</v>
       </c>
       <c r="C2048" t="s">
-        <v>159</v>
+        <v>29</v>
       </c>
       <c r="D2048" t="s">
         <v>13</v>
       </c>
       <c r="E2048" t="s">
-        <v>3218</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="2049">
       <c r="A2049" t="s">
-        <v>3219</v>
+        <v>3206</v>
       </c>
       <c r="B2049" t="s">
-        <v>3219</v>
+        <v>3206</v>
       </c>
       <c r="C2049" t="s">
-        <v>399</v>
+        <v>890</v>
       </c>
       <c r="D2049" t="s">
         <v>8</v>
       </c>
       <c r="E2049" t="s">
-        <v>3220</v>
+        <v>3207</v>
       </c>
     </row>
     <row r="2050">
       <c r="A2050" t="s">
-        <v>3219</v>
+        <v>3206</v>
       </c>
       <c r="B2050" t="s">
-        <v>3219</v>
+        <v>3208</v>
       </c>
       <c r="C2050" t="s">
-        <v>401</v>
+        <v>373</v>
       </c>
       <c r="D2050" t="s">
         <v>8</v>
       </c>
       <c r="E2050" t="s">
-        <v>3221</v>
+        <v>732</v>
       </c>
     </row>
     <row r="2051">
       <c r="A2051" t="s">
-        <v>3219</v>
+        <v>3209</v>
       </c>
       <c r="B2051" t="s">
-        <v>3219</v>
+        <v>3210</v>
       </c>
       <c r="C2051" t="s">
-        <v>53</v>
+        <v>3211</v>
       </c>
       <c r="D2051" t="s">
         <v>8</v>
       </c>
       <c r="E2051" t="s">
-        <v>3222</v>
+        <v>3212</v>
       </c>
     </row>
     <row r="2052">
       <c r="A2052" t="s">
-        <v>3223</v>
+        <v>2265</v>
       </c>
       <c r="B2052" t="s">
-        <v>3223</v>
+        <v>2265</v>
       </c>
       <c r="C2052" t="s">
-        <v>162</v>
+        <v>3211</v>
       </c>
       <c r="D2052" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2052" t="s">
-        <v>3224</v>
+        <v>3213</v>
       </c>
     </row>
     <row r="2053">
       <c r="A2053" t="s">
-        <v>3225</v>
+        <v>2265</v>
       </c>
       <c r="B2053" t="s">
-        <v>222</v>
+        <v>3214</v>
       </c>
       <c r="C2053" t="s">
-        <v>575</v>
+        <v>2265</v>
       </c>
       <c r="D2053" t="s">
         <v>8</v>
       </c>
       <c r="E2053" t="s">
-        <v>3226</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="2054">
       <c r="A2054" t="s">
-        <v>3227</v>
+        <v>3216</v>
       </c>
       <c r="B2054" t="s">
-        <v>357</v>
+        <v>3217</v>
       </c>
       <c r="C2054" t="s">
-        <v>841</v>
+        <v>159</v>
       </c>
       <c r="D2054" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2054" t="s">
-        <v>3228</v>
+        <v>3218</v>
       </c>
     </row>
     <row r="2055">
       <c r="A2055" t="s">
-        <v>3229</v>
+        <v>3219</v>
       </c>
       <c r="B2055" t="s">
-        <v>211</v>
+        <v>3219</v>
       </c>
       <c r="C2055" t="s">
-        <v>693</v>
+        <v>399</v>
       </c>
       <c r="D2055" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2055" t="s">
-        <v>3230</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="2056">
       <c r="A2056" t="s">
-        <v>3231</v>
+        <v>3219</v>
       </c>
       <c r="B2056" t="s">
-        <v>211</v>
+        <v>3219</v>
       </c>
       <c r="C2056" t="s">
-        <v>693</v>
+        <v>401</v>
       </c>
       <c r="D2056" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2056" t="s">
-        <v>3232</v>
+        <v>3221</v>
       </c>
     </row>
     <row r="2057">
       <c r="A2057" t="s">
-        <v>3233</v>
+        <v>3219</v>
       </c>
       <c r="B2057" t="s">
-        <v>335</v>
+        <v>3219</v>
       </c>
       <c r="C2057" t="s">
-        <v>2753</v>
+        <v>53</v>
       </c>
       <c r="D2057" t="s">
         <v>8</v>
       </c>
       <c r="E2057" t="s">
-        <v>3234</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="2058">
       <c r="A2058" t="s">
-        <v>3233</v>
+        <v>3223</v>
       </c>
       <c r="B2058" t="s">
-        <v>335</v>
+        <v>3223</v>
       </c>
       <c r="C2058" t="s">
-        <v>3026</v>
+        <v>162</v>
       </c>
       <c r="D2058" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2058" t="s">
-        <v>3234</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="2059">
       <c r="A2059" t="s">
-        <v>3235</v>
+        <v>3225</v>
       </c>
       <c r="B2059" t="s">
-        <v>3236</v>
+        <v>222</v>
       </c>
       <c r="C2059" t="s">
-        <v>2753</v>
+        <v>575</v>
       </c>
       <c r="D2059" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2059" t="s">
-        <v>3237</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="2060">
       <c r="A2060" t="s">
-        <v>3238</v>
+        <v>3227</v>
       </c>
       <c r="B2060" t="s">
-        <v>3239</v>
+        <v>357</v>
       </c>
       <c r="C2060" t="s">
-        <v>2753</v>
+        <v>841</v>
       </c>
       <c r="D2060" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2060" t="s">
-        <v>3240</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="2061">
       <c r="A2061" t="s">
-        <v>3241</v>
+        <v>3229</v>
       </c>
       <c r="B2061" t="s">
-        <v>3242</v>
+        <v>211</v>
       </c>
       <c r="C2061" t="s">
-        <v>492</v>
+        <v>693</v>
       </c>
       <c r="D2061" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2061" t="s">
-        <v>3243</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="2062">
       <c r="A2062" t="s">
-        <v>3244</v>
+        <v>3231</v>
       </c>
       <c r="B2062" t="s">
-        <v>3245</v>
+        <v>211</v>
       </c>
       <c r="C2062" t="s">
-        <v>492</v>
+        <v>693</v>
       </c>
       <c r="D2062" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2062" t="s">
-        <v>3246</v>
+        <v>3232</v>
       </c>
     </row>
     <row r="2063">
       <c r="A2063" t="s">
-        <v>3247</v>
+        <v>3233</v>
       </c>
       <c r="B2063" t="s">
-        <v>3248</v>
+        <v>335</v>
       </c>
       <c r="C2063" t="s">
-        <v>117</v>
+        <v>2753</v>
       </c>
       <c r="D2063" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E2063" t="s">
-        <v>3249</v>
+        <v>3234</v>
       </c>
     </row>
     <row r="2064">
       <c r="A2064" t="s">
-        <v>3247</v>
+        <v>3233</v>
       </c>
       <c r="B2064" t="s">
-        <v>3248</v>
+        <v>335</v>
       </c>
       <c r="C2064" t="s">
-        <v>121</v>
+        <v>3026</v>
       </c>
       <c r="D2064" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E2064" t="s">
-        <v>3250</v>
+        <v>3234</v>
       </c>
     </row>
     <row r="2065">
       <c r="A2065" t="s">
-        <v>291</v>
+        <v>3235</v>
       </c>
       <c r="B2065" t="s">
-        <v>291</v>
+        <v>3236</v>
       </c>
       <c r="C2065" t="s">
-        <v>35</v>
+        <v>2753</v>
       </c>
       <c r="D2065" t="s">
         <v>13</v>
       </c>
       <c r="E2065" t="s">
-        <v>3251</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="2066">
       <c r="A2066" t="s">
-        <v>291</v>
+        <v>3238</v>
       </c>
       <c r="B2066" t="s">
-        <v>291</v>
+        <v>3239</v>
       </c>
       <c r="C2066" t="s">
-        <v>373</v>
+        <v>2753</v>
       </c>
       <c r="D2066" t="s">
         <v>13</v>
       </c>
       <c r="E2066" t="s">
-        <v>3252</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="2067">
       <c r="A2067" t="s">
-        <v>291</v>
+        <v>3241</v>
       </c>
       <c r="B2067" t="s">
-        <v>291</v>
+        <v>3242</v>
       </c>
       <c r="C2067" t="s">
-        <v>911</v>
+        <v>492</v>
       </c>
       <c r="D2067" t="s">
         <v>17</v>
       </c>
       <c r="E2067" t="s">
-        <v>3253</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="2068">
       <c r="A2068" t="s">
-        <v>3254</v>
+        <v>3244</v>
       </c>
       <c r="B2068" t="s">
-        <v>211</v>
+        <v>3245</v>
       </c>
       <c r="C2068" t="s">
-        <v>735</v>
+        <v>492</v>
       </c>
       <c r="D2068" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2068" t="s">
-        <v>3255</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="2069">
       <c r="A2069" t="s">
-        <v>3256</v>
+        <v>3247</v>
       </c>
       <c r="B2069" t="s">
-        <v>211</v>
+        <v>3248</v>
       </c>
       <c r="C2069" t="s">
-        <v>735</v>
+        <v>117</v>
       </c>
       <c r="D2069" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2069" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="2070">
       <c r="A2070" t="s">
-        <v>3258</v>
+        <v>3247</v>
       </c>
       <c r="B2070" t="s">
-        <v>211</v>
+        <v>3248</v>
       </c>
       <c r="C2070" t="s">
-        <v>735</v>
+        <v>121</v>
       </c>
       <c r="D2070" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2070" t="s">
-        <v>3259</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="2071">
       <c r="A2071" t="s">
-        <v>3260</v>
+        <v>291</v>
       </c>
       <c r="B2071" t="s">
         <v>291</v>
       </c>
       <c r="C2071" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="D2071" t="s">
         <v>13</v>
       </c>
       <c r="E2071" t="s">
-        <v>3261</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="2072">
       <c r="A2072" t="s">
-        <v>3262</v>
+        <v>291</v>
       </c>
       <c r="B2072" t="s">
-        <v>3262</v>
+        <v>291</v>
       </c>
       <c r="C2072" t="s">
-        <v>1935</v>
+        <v>373</v>
       </c>
       <c r="D2072" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2072" t="s">
-        <v>3263</v>
+        <v>3252</v>
       </c>
     </row>
     <row r="2073">
       <c r="A2073" t="s">
-        <v>3262</v>
+        <v>291</v>
       </c>
       <c r="B2073" t="s">
-        <v>3262</v>
+        <v>291</v>
       </c>
       <c r="C2073" t="s">
-        <v>922</v>
+        <v>911</v>
       </c>
       <c r="D2073" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E2073" t="s">
-        <v>3263</v>
+        <v>3253</v>
       </c>
     </row>
     <row r="2074">
       <c r="A2074" t="s">
-        <v>3264</v>
+        <v>3254</v>
       </c>
       <c r="B2074" t="s">
-        <v>3265</v>
+        <v>211</v>
       </c>
       <c r="C2074" t="s">
-        <v>373</v>
+        <v>735</v>
       </c>
       <c r="D2074" t="s">
         <v>13</v>
       </c>
       <c r="E2074" t="s">
-        <v>3266</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="2075">
       <c r="A2075" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="B2075" t="s">
-        <v>3267</v>
+        <v>211</v>
       </c>
       <c r="C2075" t="s">
-        <v>103</v>
+        <v>735</v>
       </c>
       <c r="D2075" t="s">
         <v>13</v>
       </c>
       <c r="E2075" t="s">
-        <v>3266</v>
+        <v>3257</v>
       </c>
     </row>
     <row r="2076">
       <c r="A2076" t="s">
-        <v>3268</v>
+        <v>3258</v>
       </c>
       <c r="B2076" t="s">
-        <v>3269</v>
+        <v>211</v>
       </c>
       <c r="C2076" t="s">
-        <v>555</v>
+        <v>735</v>
       </c>
       <c r="D2076" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2076" t="s">
-        <v>3270</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="2077">
       <c r="A2077" t="s">
-        <v>3271</v>
+        <v>3260</v>
       </c>
       <c r="B2077" t="s">
-        <v>3272</v>
+        <v>291</v>
       </c>
       <c r="C2077" t="s">
-        <v>455</v>
+        <v>103</v>
       </c>
       <c r="D2077" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2077" t="s">
-        <v>3273</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="2078">
       <c r="A2078" t="s">
-        <v>3271</v>
+        <v>3262</v>
       </c>
       <c r="B2078" t="s">
-        <v>3272</v>
+        <v>3262</v>
       </c>
       <c r="C2078" t="s">
-        <v>458</v>
+        <v>1935</v>
       </c>
       <c r="D2078" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E2078" t="s">
-        <v>3274</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="2079">
       <c r="A2079" t="s">
-        <v>3275</v>
+        <v>3262</v>
       </c>
       <c r="B2079" t="s">
-        <v>291</v>
+        <v>3262</v>
       </c>
       <c r="C2079" t="s">
-        <v>115</v>
+        <v>922</v>
       </c>
       <c r="D2079" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2079" t="s">
-        <v>3276</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="2080">
       <c r="A2080" t="s">
-        <v>3277</v>
+        <v>3264</v>
       </c>
       <c r="B2080" t="s">
-        <v>3277</v>
+        <v>3265</v>
       </c>
       <c r="C2080" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="D2080" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2080" t="s">
-        <v>3278</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="2081">
       <c r="A2081" t="s">
-        <v>3277</v>
+        <v>3264</v>
       </c>
       <c r="B2081" t="s">
-        <v>3277</v>
+        <v>3267</v>
       </c>
       <c r="C2081" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="D2081" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2081" t="s">
-        <v>3278</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="2082">
       <c r="A2082" t="s">
-        <v>3279</v>
+        <v>3268</v>
       </c>
       <c r="B2082" t="s">
-        <v>191</v>
+        <v>3269</v>
       </c>
       <c r="C2082" t="s">
-        <v>57</v>
+        <v>555</v>
       </c>
       <c r="D2082" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2082" t="s">
-        <v>3280</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="2083">
       <c r="A2083" t="s">
-        <v>3281</v>
+        <v>3271</v>
       </c>
       <c r="B2083" t="s">
-        <v>191</v>
+        <v>3272</v>
       </c>
       <c r="C2083" t="s">
-        <v>31</v>
+        <v>455</v>
       </c>
       <c r="D2083" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2083" t="s">
-        <v>3282</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="2084">
       <c r="A2084" t="s">
-        <v>3281</v>
+        <v>3271</v>
       </c>
       <c r="B2084" t="s">
-        <v>191</v>
+        <v>3272</v>
       </c>
       <c r="C2084" t="s">
-        <v>799</v>
+        <v>458</v>
       </c>
       <c r="D2084" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2084" t="s">
-        <v>3283</v>
+        <v>3274</v>
       </c>
     </row>
     <row r="2085">
       <c r="A2085" t="s">
-        <v>3284</v>
+        <v>3275</v>
       </c>
       <c r="B2085" t="s">
-        <v>3285</v>
+        <v>291</v>
       </c>
       <c r="C2085" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D2085" t="s">
         <v>13</v>
       </c>
       <c r="E2085" t="s">
-        <v>3286</v>
+        <v>3276</v>
       </c>
     </row>
     <row r="2086">
       <c r="A2086" t="s">
-        <v>3287</v>
+        <v>3277</v>
       </c>
       <c r="B2086" t="s">
-        <v>3285</v>
+        <v>3277</v>
       </c>
       <c r="C2086" t="s">
-        <v>117</v>
+        <v>399</v>
       </c>
       <c r="D2086" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2086" t="s">
-        <v>3288</v>
+        <v>3278</v>
       </c>
     </row>
     <row r="2087">
       <c r="A2087" t="s">
+        <v>3277</v>
+      </c>
+      <c r="B2087" t="s">
+        <v>3277</v>
+      </c>
+      <c r="C2087" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2087" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2087" t="s">
+        <v>3278</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="s">
+        <v>3279</v>
+      </c>
+      <c r="B2088" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2088" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2088" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2088" t="s">
+        <v>3280</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="s">
+        <v>3281</v>
+      </c>
+      <c r="B2089" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2089" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2089" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2089" t="s">
+        <v>3282</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="s">
+        <v>3281</v>
+      </c>
+      <c r="B2090" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2090" t="s">
+        <v>799</v>
+      </c>
+      <c r="D2090" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2090" t="s">
+        <v>3283</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="s">
+        <v>3284</v>
+      </c>
+      <c r="B2091" t="s">
+        <v>3285</v>
+      </c>
+      <c r="C2091" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2091" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2091" t="s">
+        <v>3286</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="s">
+        <v>3287</v>
+      </c>
+      <c r="B2092" t="s">
+        <v>3285</v>
+      </c>
+      <c r="C2092" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2092" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2092" t="s">
+        <v>3288</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="s">
         <v>3289</v>
       </c>
-      <c r="B2087" t="s">
+      <c r="B2093" t="s">
         <v>2118</v>
       </c>
-      <c r="C2087" t="s">
+      <c r="C2093" t="s">
         <v>378</v>
       </c>
-      <c r="D2087" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2087" t="s">
+      <c r="D2093" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2093" t="s">
         <v>3290</v>
       </c>
     </row>

--- a/MetaEdOutput/Documentation/DataDictionary/XmlDataDictionary.xlsx
+++ b/MetaEdOutput/Documentation/DataDictionary/XmlDataDictionary.xlsx
@@ -12251,6 +12251,9 @@
   </si>
   <si>
     <t>maxLength: 2048</t>
+  </si>
+  <si>
+    <t>maxLength: 256</t>
   </si>
   <si>
     <t>EXTENSION-ServiceComplianceDescriptorReferenceType</t>
@@ -43810,146 +43813,146 @@
     </row>
     <row r="1836">
       <c r="A1836" t="s">
-        <v>2956</v>
+        <v>2962</v>
       </c>
       <c r="B1836" t="s">
-        <v>2954</v>
+        <v>1632</v>
       </c>
       <c r="C1836" t="s">
-        <v>1608</v>
+        <v>2963</v>
       </c>
       <c r="D1836" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1836" t="s">
-        <v>2957</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="1837">
       <c r="A1837" t="s">
-        <v>2956</v>
+        <v>343</v>
       </c>
       <c r="B1837" t="s">
-        <v>2954</v>
+        <v>343</v>
       </c>
       <c r="C1837" t="s">
-        <v>1619</v>
+        <v>121</v>
       </c>
       <c r="D1837" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E1837" t="s">
-        <v>2958</v>
+        <v>2965</v>
       </c>
     </row>
     <row r="1838">
       <c r="A1838" t="s">
-        <v>2956</v>
+        <v>2966</v>
       </c>
       <c r="B1838" t="s">
-        <v>2954</v>
+        <v>2967</v>
       </c>
       <c r="C1838" t="s">
-        <v>1624</v>
+        <v>343</v>
       </c>
       <c r="D1838" t="s">
         <v>8</v>
       </c>
       <c r="E1838" t="s">
-        <v>2959</v>
+        <v>2965</v>
       </c>
     </row>
     <row r="1839">
       <c r="A1839" t="s">
-        <v>2956</v>
+        <v>2968</v>
       </c>
       <c r="B1839" t="s">
-        <v>2954</v>
+        <v>2969</v>
       </c>
       <c r="C1839" t="s">
-        <v>1631</v>
+        <v>2970</v>
       </c>
       <c r="D1839" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1839" t="s">
-        <v>2960</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="1840">
       <c r="A1840" t="s">
-        <v>2956</v>
+        <v>932</v>
       </c>
       <c r="B1840" t="s">
-        <v>2954</v>
+        <v>932</v>
       </c>
       <c r="C1840" t="s">
-        <v>1632</v>
+        <v>121</v>
       </c>
       <c r="D1840" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E1840" t="s">
-        <v>2961</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="1841">
       <c r="A1841" t="s">
-        <v>2962</v>
+        <v>2973</v>
       </c>
       <c r="B1841" t="s">
-        <v>1632</v>
+        <v>1753</v>
       </c>
       <c r="C1841" t="s">
-        <v>2963</v>
+        <v>2974</v>
       </c>
       <c r="D1841" t="s">
         <v>13</v>
       </c>
       <c r="E1841" t="s">
-        <v>2964</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="1842">
       <c r="A1842" t="s">
-        <v>343</v>
+        <v>2976</v>
       </c>
       <c r="B1842" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="C1842" t="s">
-        <v>121</v>
+        <v>2977</v>
       </c>
       <c r="D1842" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E1842" t="s">
-        <v>2965</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="1843">
       <c r="A1843" t="s">
-        <v>2966</v>
+        <v>2979</v>
       </c>
       <c r="B1843" t="s">
-        <v>2967</v>
+        <v>439</v>
       </c>
       <c r="C1843" t="s">
-        <v>343</v>
+        <v>2980</v>
       </c>
       <c r="D1843" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1843" t="s">
-        <v>2965</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="1844">
       <c r="A1844" t="s">
-        <v>2968</v>
+        <v>2982</v>
       </c>
       <c r="B1844" t="s">
-        <v>2969</v>
+        <v>478</v>
       </c>
       <c r="C1844" t="s">
         <v>2970</v>
@@ -43958,228 +43961,228 @@
         <v>13</v>
       </c>
       <c r="E1844" t="s">
-        <v>2971</v>
+        <v>2983</v>
       </c>
     </row>
     <row r="1845">
       <c r="A1845" t="s">
-        <v>932</v>
+        <v>2984</v>
       </c>
       <c r="B1845" t="s">
-        <v>932</v>
+        <v>440</v>
       </c>
       <c r="C1845" t="s">
-        <v>121</v>
+        <v>2985</v>
       </c>
       <c r="D1845" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E1845" t="s">
-        <v>2972</v>
+        <v>2986</v>
       </c>
     </row>
     <row r="1846">
       <c r="A1846" t="s">
-        <v>2973</v>
+        <v>2987</v>
       </c>
       <c r="B1846" t="s">
-        <v>1753</v>
+        <v>441</v>
       </c>
       <c r="C1846" t="s">
-        <v>2974</v>
+        <v>2988</v>
       </c>
       <c r="D1846" t="s">
         <v>13</v>
       </c>
       <c r="E1846" t="s">
-        <v>2975</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="1847">
       <c r="A1847" t="s">
-        <v>2976</v>
+        <v>139</v>
       </c>
       <c r="B1847" t="s">
-        <v>365</v>
+        <v>139</v>
       </c>
       <c r="C1847" t="s">
-        <v>2977</v>
+        <v>57</v>
       </c>
       <c r="D1847" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E1847" t="s">
-        <v>2978</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="1848">
       <c r="A1848" t="s">
-        <v>2979</v>
+        <v>2991</v>
       </c>
       <c r="B1848" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C1848" t="s">
-        <v>2980</v>
+        <v>2992</v>
       </c>
       <c r="D1848" t="s">
         <v>13</v>
       </c>
       <c r="E1848" t="s">
-        <v>2981</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="1849">
       <c r="A1849" t="s">
-        <v>2982</v>
+        <v>2994</v>
       </c>
       <c r="B1849" t="s">
-        <v>478</v>
+        <v>367</v>
       </c>
       <c r="C1849" t="s">
-        <v>2970</v>
+        <v>2995</v>
       </c>
       <c r="D1849" t="s">
         <v>13</v>
       </c>
       <c r="E1849" t="s">
-        <v>2983</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="1850">
       <c r="A1850" t="s">
-        <v>2984</v>
+        <v>2997</v>
       </c>
       <c r="B1850" t="s">
-        <v>440</v>
+        <v>1303</v>
       </c>
       <c r="C1850" t="s">
-        <v>2985</v>
+        <v>2998</v>
       </c>
       <c r="D1850" t="s">
         <v>13</v>
       </c>
       <c r="E1850" t="s">
-        <v>2986</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="1851">
       <c r="A1851" t="s">
-        <v>2987</v>
+        <v>3000</v>
       </c>
       <c r="B1851" t="s">
-        <v>441</v>
+        <v>64</v>
       </c>
       <c r="C1851" t="s">
-        <v>2988</v>
+        <v>415</v>
       </c>
       <c r="D1851" t="s">
         <v>13</v>
       </c>
       <c r="E1851" t="s">
-        <v>2989</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="1852">
       <c r="A1852" t="s">
-        <v>139</v>
+        <v>3000</v>
       </c>
       <c r="B1852" t="s">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="C1852" t="s">
-        <v>57</v>
+        <v>419</v>
       </c>
       <c r="D1852" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E1852" t="s">
-        <v>2990</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="1853">
       <c r="A1853" t="s">
-        <v>2991</v>
+        <v>3003</v>
       </c>
       <c r="B1853" t="s">
-        <v>442</v>
+        <v>2970</v>
       </c>
       <c r="C1853" t="s">
-        <v>2992</v>
+        <v>98</v>
       </c>
       <c r="D1853" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1853" t="s">
-        <v>2993</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="1854">
       <c r="A1854" t="s">
-        <v>2994</v>
+        <v>3003</v>
       </c>
       <c r="B1854" t="s">
-        <v>367</v>
+        <v>2970</v>
       </c>
       <c r="C1854" t="s">
-        <v>2995</v>
+        <v>1347</v>
       </c>
       <c r="D1854" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1854" t="s">
-        <v>2996</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1855">
       <c r="A1855" t="s">
-        <v>2997</v>
+        <v>3003</v>
       </c>
       <c r="B1855" t="s">
-        <v>1303</v>
+        <v>2970</v>
       </c>
       <c r="C1855" t="s">
-        <v>2998</v>
+        <v>1137</v>
       </c>
       <c r="D1855" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1855" t="s">
-        <v>2999</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="1856">
       <c r="A1856" t="s">
-        <v>3000</v>
+        <v>3003</v>
       </c>
       <c r="B1856" t="s">
-        <v>64</v>
+        <v>2970</v>
       </c>
       <c r="C1856" t="s">
-        <v>415</v>
+        <v>1003</v>
       </c>
       <c r="D1856" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1856" t="s">
-        <v>3001</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="1857">
       <c r="A1857" t="s">
-        <v>3000</v>
+        <v>3003</v>
       </c>
       <c r="B1857" t="s">
-        <v>64</v>
+        <v>2970</v>
       </c>
       <c r="C1857" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
       <c r="D1857" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1857" t="s">
-        <v>3002</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="1858">
@@ -44190,13 +44193,13 @@
         <v>2970</v>
       </c>
       <c r="C1858" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="D1858" t="s">
         <v>8</v>
       </c>
       <c r="E1858" t="s">
-        <v>3004</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="1859">
@@ -44207,13 +44210,13 @@
         <v>2970</v>
       </c>
       <c r="C1859" t="s">
-        <v>1347</v>
+        <v>677</v>
       </c>
       <c r="D1859" t="s">
         <v>8</v>
       </c>
       <c r="E1859" t="s">
-        <v>3005</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="1860">
@@ -44224,13 +44227,13 @@
         <v>2970</v>
       </c>
       <c r="C1860" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="D1860" t="s">
         <v>8</v>
       </c>
       <c r="E1860" t="s">
-        <v>3006</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="1861">
@@ -44241,13 +44244,13 @@
         <v>2970</v>
       </c>
       <c r="C1861" t="s">
-        <v>1003</v>
+        <v>347</v>
       </c>
       <c r="D1861" t="s">
         <v>8</v>
       </c>
       <c r="E1861" t="s">
-        <v>3007</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="1862">
@@ -44258,13 +44261,13 @@
         <v>2970</v>
       </c>
       <c r="C1862" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="D1862" t="s">
         <v>8</v>
       </c>
       <c r="E1862" t="s">
-        <v>3008</v>
+        <v>3012</v>
       </c>
     </row>
     <row r="1863">
@@ -44275,13 +44278,13 @@
         <v>2970</v>
       </c>
       <c r="C1863" t="s">
-        <v>57</v>
+        <v>360</v>
       </c>
       <c r="D1863" t="s">
         <v>8</v>
       </c>
       <c r="E1863" t="s">
-        <v>3009</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="1864">
@@ -44292,13 +44295,13 @@
         <v>2970</v>
       </c>
       <c r="C1864" t="s">
-        <v>677</v>
+        <v>362</v>
       </c>
       <c r="D1864" t="s">
         <v>8</v>
       </c>
       <c r="E1864" t="s">
-        <v>3010</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="1865">
@@ -44309,13 +44312,13 @@
         <v>2970</v>
       </c>
       <c r="C1865" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="D1865" t="s">
         <v>8</v>
       </c>
       <c r="E1865" t="s">
-        <v>3009</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="1866">
@@ -44326,13 +44329,13 @@
         <v>2970</v>
       </c>
       <c r="C1866" t="s">
-        <v>347</v>
+        <v>207</v>
       </c>
       <c r="D1866" t="s">
         <v>8</v>
       </c>
       <c r="E1866" t="s">
-        <v>3011</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="1867">
@@ -44343,13 +44346,13 @@
         <v>2970</v>
       </c>
       <c r="C1867" t="s">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="D1867" t="s">
         <v>8</v>
       </c>
       <c r="E1867" t="s">
-        <v>3012</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="1868">
@@ -44360,13 +44363,13 @@
         <v>2970</v>
       </c>
       <c r="C1868" t="s">
-        <v>360</v>
+        <v>2753</v>
       </c>
       <c r="D1868" t="s">
         <v>8</v>
       </c>
       <c r="E1868" t="s">
-        <v>3013</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="1869">
@@ -44377,13 +44380,13 @@
         <v>2970</v>
       </c>
       <c r="C1869" t="s">
-        <v>362</v>
+        <v>706</v>
       </c>
       <c r="D1869" t="s">
         <v>8</v>
       </c>
       <c r="E1869" t="s">
-        <v>3013</v>
+        <v>3016</v>
       </c>
     </row>
     <row r="1870">
@@ -44394,13 +44397,13 @@
         <v>2970</v>
       </c>
       <c r="C1870" t="s">
-        <v>1144</v>
+        <v>413</v>
       </c>
       <c r="D1870" t="s">
         <v>8</v>
       </c>
       <c r="E1870" t="s">
-        <v>3014</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="1871">
@@ -44411,13 +44414,13 @@
         <v>2970</v>
       </c>
       <c r="C1871" t="s">
-        <v>207</v>
+        <v>423</v>
       </c>
       <c r="D1871" t="s">
         <v>8</v>
       </c>
       <c r="E1871" t="s">
-        <v>3013</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="1872">
@@ -44428,13 +44431,13 @@
         <v>2970</v>
       </c>
       <c r="C1872" t="s">
-        <v>209</v>
+        <v>703</v>
       </c>
       <c r="D1872" t="s">
         <v>8</v>
       </c>
       <c r="E1872" t="s">
-        <v>3013</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="1873">
@@ -44445,13 +44448,13 @@
         <v>2970</v>
       </c>
       <c r="C1873" t="s">
-        <v>2753</v>
+        <v>458</v>
       </c>
       <c r="D1873" t="s">
         <v>8</v>
       </c>
       <c r="E1873" t="s">
-        <v>3015</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="1874">
@@ -44462,13 +44465,13 @@
         <v>2970</v>
       </c>
       <c r="C1874" t="s">
-        <v>706</v>
+        <v>1000</v>
       </c>
       <c r="D1874" t="s">
         <v>8</v>
       </c>
       <c r="E1874" t="s">
-        <v>3016</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="1875">
@@ -44479,13 +44482,13 @@
         <v>2970</v>
       </c>
       <c r="C1875" t="s">
-        <v>413</v>
+        <v>121</v>
       </c>
       <c r="D1875" t="s">
         <v>8</v>
       </c>
       <c r="E1875" t="s">
-        <v>3017</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1876">
@@ -44496,13 +44499,13 @@
         <v>2970</v>
       </c>
       <c r="C1876" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D1876" t="s">
         <v>8</v>
       </c>
       <c r="E1876" t="s">
-        <v>3018</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1877">
@@ -44513,13 +44516,13 @@
         <v>2970</v>
       </c>
       <c r="C1877" t="s">
-        <v>703</v>
+        <v>634</v>
       </c>
       <c r="D1877" t="s">
         <v>8</v>
       </c>
       <c r="E1877" t="s">
-        <v>3019</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="1878">
@@ -44530,13 +44533,13 @@
         <v>2970</v>
       </c>
       <c r="C1878" t="s">
-        <v>458</v>
+        <v>172</v>
       </c>
       <c r="D1878" t="s">
         <v>8</v>
       </c>
       <c r="E1878" t="s">
-        <v>3020</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="1879">
@@ -44547,13 +44550,13 @@
         <v>2970</v>
       </c>
       <c r="C1879" t="s">
-        <v>1000</v>
+        <v>354</v>
       </c>
       <c r="D1879" t="s">
         <v>8</v>
       </c>
       <c r="E1879" t="s">
-        <v>3020</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="1880">
@@ -44564,13 +44567,13 @@
         <v>2970</v>
       </c>
       <c r="C1880" t="s">
-        <v>121</v>
+        <v>693</v>
       </c>
       <c r="D1880" t="s">
         <v>8</v>
       </c>
       <c r="E1880" t="s">
-        <v>3021</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="1881">
@@ -44581,13 +44584,13 @@
         <v>2970</v>
       </c>
       <c r="C1881" t="s">
-        <v>425</v>
+        <v>980</v>
       </c>
       <c r="D1881" t="s">
         <v>8</v>
       </c>
       <c r="E1881" t="s">
-        <v>3021</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="1882">
@@ -44598,13 +44601,13 @@
         <v>2970</v>
       </c>
       <c r="C1882" t="s">
-        <v>634</v>
+        <v>429</v>
       </c>
       <c r="D1882" t="s">
         <v>8</v>
       </c>
       <c r="E1882" t="s">
-        <v>3022</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="1883">
@@ -44615,13 +44618,13 @@
         <v>2970</v>
       </c>
       <c r="C1883" t="s">
-        <v>172</v>
+        <v>1352</v>
       </c>
       <c r="D1883" t="s">
         <v>8</v>
       </c>
       <c r="E1883" t="s">
-        <v>3023</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1884">
@@ -44632,13 +44635,13 @@
         <v>2970</v>
       </c>
       <c r="C1884" t="s">
-        <v>354</v>
+        <v>1167</v>
       </c>
       <c r="D1884" t="s">
         <v>8</v>
       </c>
       <c r="E1884" t="s">
-        <v>3024</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="1885">
@@ -44649,13 +44652,13 @@
         <v>2970</v>
       </c>
       <c r="C1885" t="s">
-        <v>693</v>
+        <v>2536</v>
       </c>
       <c r="D1885" t="s">
         <v>8</v>
       </c>
       <c r="E1885" t="s">
-        <v>3025</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="1886">
@@ -44666,13 +44669,13 @@
         <v>2970</v>
       </c>
       <c r="C1886" t="s">
-        <v>980</v>
+        <v>1170</v>
       </c>
       <c r="D1886" t="s">
         <v>8</v>
       </c>
       <c r="E1886" t="s">
-        <v>3004</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="1887">
@@ -44683,13 +44686,13 @@
         <v>2970</v>
       </c>
       <c r="C1887" t="s">
-        <v>429</v>
+        <v>312</v>
       </c>
       <c r="D1887" t="s">
         <v>8</v>
       </c>
       <c r="E1887" t="s">
-        <v>3017</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="1888">
@@ -44700,13 +44703,13 @@
         <v>2970</v>
       </c>
       <c r="C1888" t="s">
-        <v>1352</v>
+        <v>435</v>
       </c>
       <c r="D1888" t="s">
         <v>8</v>
       </c>
       <c r="E1888" t="s">
-        <v>3005</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="1889">
@@ -44717,13 +44720,13 @@
         <v>2970</v>
       </c>
       <c r="C1889" t="s">
-        <v>1167</v>
+        <v>689</v>
       </c>
       <c r="D1889" t="s">
         <v>8</v>
       </c>
       <c r="E1889" t="s">
-        <v>3006</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="1890">
@@ -44734,13 +44737,13 @@
         <v>2970</v>
       </c>
       <c r="C1890" t="s">
-        <v>2536</v>
+        <v>709</v>
       </c>
       <c r="D1890" t="s">
         <v>8</v>
       </c>
       <c r="E1890" t="s">
-        <v>3007</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="1891">
@@ -44751,13 +44754,13 @@
         <v>2970</v>
       </c>
       <c r="C1891" t="s">
-        <v>1170</v>
+        <v>436</v>
       </c>
       <c r="D1891" t="s">
         <v>8</v>
       </c>
       <c r="E1891" t="s">
-        <v>3008</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="1892">
@@ -44768,13 +44771,13 @@
         <v>2970</v>
       </c>
       <c r="C1892" t="s">
-        <v>312</v>
+        <v>460</v>
       </c>
       <c r="D1892" t="s">
         <v>8</v>
       </c>
       <c r="E1892" t="s">
-        <v>3009</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="1893">
@@ -44785,13 +44788,13 @@
         <v>2970</v>
       </c>
       <c r="C1893" t="s">
-        <v>435</v>
+        <v>1008</v>
       </c>
       <c r="D1893" t="s">
         <v>8</v>
       </c>
       <c r="E1893" t="s">
-        <v>3018</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="1894">
@@ -44802,13 +44805,13 @@
         <v>2970</v>
       </c>
       <c r="C1894" t="s">
-        <v>689</v>
+        <v>1171</v>
       </c>
       <c r="D1894" t="s">
         <v>8</v>
       </c>
       <c r="E1894" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="1895">
@@ -44819,13 +44822,13 @@
         <v>2970</v>
       </c>
       <c r="C1895" t="s">
-        <v>709</v>
+        <v>1172</v>
       </c>
       <c r="D1895" t="s">
         <v>8</v>
       </c>
       <c r="E1895" t="s">
-        <v>3019</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1896">
@@ -44836,13 +44839,13 @@
         <v>2970</v>
       </c>
       <c r="C1896" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D1896" t="s">
         <v>8</v>
       </c>
       <c r="E1896" t="s">
-        <v>3017</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1897">
@@ -44853,13 +44856,13 @@
         <v>2970</v>
       </c>
       <c r="C1897" t="s">
-        <v>460</v>
+        <v>1503</v>
       </c>
       <c r="D1897" t="s">
         <v>8</v>
       </c>
       <c r="E1897" t="s">
-        <v>3020</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="1898">
@@ -44870,13 +44873,13 @@
         <v>2970</v>
       </c>
       <c r="C1898" t="s">
-        <v>1008</v>
+        <v>1173</v>
       </c>
       <c r="D1898" t="s">
         <v>8</v>
       </c>
       <c r="E1898" t="s">
-        <v>3020</v>
+        <v>3012</v>
       </c>
     </row>
     <row r="1899">
@@ -44887,13 +44890,13 @@
         <v>2970</v>
       </c>
       <c r="C1899" t="s">
-        <v>1171</v>
+        <v>438</v>
       </c>
       <c r="D1899" t="s">
         <v>8</v>
       </c>
       <c r="E1899" t="s">
-        <v>3009</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="1900">
@@ -44904,13 +44907,13 @@
         <v>2970</v>
       </c>
       <c r="C1900" t="s">
-        <v>1172</v>
+        <v>1753</v>
       </c>
       <c r="D1900" t="s">
         <v>8</v>
       </c>
       <c r="E1900" t="s">
-        <v>3021</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="1901">
@@ -44921,13 +44924,13 @@
         <v>2970</v>
       </c>
       <c r="C1901" t="s">
-        <v>437</v>
+        <v>365</v>
       </c>
       <c r="D1901" t="s">
         <v>8</v>
       </c>
       <c r="E1901" t="s">
-        <v>3021</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="1902">
@@ -44938,13 +44941,13 @@
         <v>2970</v>
       </c>
       <c r="C1902" t="s">
-        <v>1503</v>
+        <v>439</v>
       </c>
       <c r="D1902" t="s">
         <v>8</v>
       </c>
       <c r="E1902" t="s">
-        <v>3011</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="1903">
@@ -44955,13 +44958,13 @@
         <v>2970</v>
       </c>
       <c r="C1903" t="s">
-        <v>1173</v>
+        <v>440</v>
       </c>
       <c r="D1903" t="s">
         <v>8</v>
       </c>
       <c r="E1903" t="s">
-        <v>3012</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="1904">
@@ -44972,7 +44975,7 @@
         <v>2970</v>
       </c>
       <c r="C1904" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D1904" t="s">
         <v>8</v>
@@ -44989,13 +44992,13 @@
         <v>2970</v>
       </c>
       <c r="C1905" t="s">
-        <v>1753</v>
+        <v>442</v>
       </c>
       <c r="D1905" t="s">
         <v>8</v>
       </c>
       <c r="E1905" t="s">
-        <v>3022</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="1906">
@@ -45006,7 +45009,7 @@
         <v>2970</v>
       </c>
       <c r="C1906" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D1906" t="s">
         <v>8</v>
@@ -45023,13 +45026,13 @@
         <v>2970</v>
       </c>
       <c r="C1907" t="s">
-        <v>439</v>
+        <v>1303</v>
       </c>
       <c r="D1907" t="s">
         <v>8</v>
       </c>
       <c r="E1907" t="s">
-        <v>3017</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="1908">
@@ -45040,13 +45043,13 @@
         <v>2970</v>
       </c>
       <c r="C1908" t="s">
-        <v>440</v>
+        <v>1287</v>
       </c>
       <c r="D1908" t="s">
         <v>8</v>
       </c>
       <c r="E1908" t="s">
-        <v>3017</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="1909">
@@ -45057,13 +45060,13 @@
         <v>2970</v>
       </c>
       <c r="C1909" t="s">
-        <v>441</v>
+        <v>368</v>
       </c>
       <c r="D1909" t="s">
         <v>8</v>
       </c>
       <c r="E1909" t="s">
-        <v>3017</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="1910">
@@ -45074,7 +45077,7 @@
         <v>2970</v>
       </c>
       <c r="C1910" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D1910" t="s">
         <v>8</v>
@@ -45091,13 +45094,13 @@
         <v>2970</v>
       </c>
       <c r="C1911" t="s">
-        <v>367</v>
+        <v>444</v>
       </c>
       <c r="D1911" t="s">
         <v>8</v>
       </c>
       <c r="E1911" t="s">
-        <v>3013</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="1912">
@@ -45108,13 +45111,13 @@
         <v>2970</v>
       </c>
       <c r="C1912" t="s">
-        <v>1303</v>
+        <v>445</v>
       </c>
       <c r="D1912" t="s">
         <v>8</v>
       </c>
       <c r="E1912" t="s">
-        <v>3014</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="1913">
@@ -45125,13 +45128,13 @@
         <v>2970</v>
       </c>
       <c r="C1913" t="s">
-        <v>1287</v>
+        <v>369</v>
       </c>
       <c r="D1913" t="s">
         <v>8</v>
       </c>
       <c r="E1913" t="s">
-        <v>3023</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="1914">
@@ -45142,13 +45145,13 @@
         <v>2970</v>
       </c>
       <c r="C1914" t="s">
-        <v>368</v>
+        <v>446</v>
       </c>
       <c r="D1914" t="s">
         <v>8</v>
       </c>
       <c r="E1914" t="s">
-        <v>3013</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="1915">
@@ -45159,13 +45162,13 @@
         <v>2970</v>
       </c>
       <c r="C1915" t="s">
-        <v>443</v>
+        <v>697</v>
       </c>
       <c r="D1915" t="s">
         <v>8</v>
       </c>
       <c r="E1915" t="s">
-        <v>3017</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="1916">
@@ -45176,7 +45179,7 @@
         <v>2970</v>
       </c>
       <c r="C1916" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D1916" t="s">
         <v>8</v>
@@ -45193,13 +45196,13 @@
         <v>2970</v>
       </c>
       <c r="C1917" t="s">
-        <v>445</v>
+        <v>3026</v>
       </c>
       <c r="D1917" t="s">
         <v>8</v>
       </c>
       <c r="E1917" t="s">
-        <v>3024</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="1918">
@@ -45210,13 +45213,13 @@
         <v>2970</v>
       </c>
       <c r="C1918" t="s">
-        <v>369</v>
+        <v>1176</v>
       </c>
       <c r="D1918" t="s">
         <v>8</v>
       </c>
       <c r="E1918" t="s">
-        <v>3013</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1919">
@@ -45227,13 +45230,13 @@
         <v>2970</v>
       </c>
       <c r="C1919" t="s">
-        <v>446</v>
+        <v>1460</v>
       </c>
       <c r="D1919" t="s">
         <v>8</v>
       </c>
       <c r="E1919" t="s">
-        <v>3017</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1920">
@@ -45244,13 +45247,13 @@
         <v>2970</v>
       </c>
       <c r="C1920" t="s">
-        <v>697</v>
+        <v>1388</v>
       </c>
       <c r="D1920" t="s">
         <v>8</v>
       </c>
       <c r="E1920" t="s">
-        <v>3025</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1921">
@@ -45261,13 +45264,13 @@
         <v>2970</v>
       </c>
       <c r="C1921" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="D1921" t="s">
         <v>8</v>
       </c>
       <c r="E1921" t="s">
-        <v>3017</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1922">
@@ -45278,13 +45281,13 @@
         <v>2970</v>
       </c>
       <c r="C1922" t="s">
-        <v>3026</v>
+        <v>61</v>
       </c>
       <c r="D1922" t="s">
         <v>8</v>
       </c>
       <c r="E1922" t="s">
-        <v>3015</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1923">
@@ -45295,7 +45298,7 @@
         <v>2970</v>
       </c>
       <c r="C1923" t="s">
-        <v>1176</v>
+        <v>966</v>
       </c>
       <c r="D1923" t="s">
         <v>8</v>
@@ -45312,7 +45315,7 @@
         <v>2970</v>
       </c>
       <c r="C1924" t="s">
-        <v>1460</v>
+        <v>1581</v>
       </c>
       <c r="D1924" t="s">
         <v>8</v>
@@ -45329,7 +45332,7 @@
         <v>2970</v>
       </c>
       <c r="C1925" t="s">
-        <v>1388</v>
+        <v>1178</v>
       </c>
       <c r="D1925" t="s">
         <v>8</v>
@@ -45346,7 +45349,7 @@
         <v>2970</v>
       </c>
       <c r="C1926" t="s">
-        <v>452</v>
+        <v>1608</v>
       </c>
       <c r="D1926" t="s">
         <v>8</v>
@@ -45363,7 +45366,7 @@
         <v>2970</v>
       </c>
       <c r="C1927" t="s">
-        <v>61</v>
+        <v>1619</v>
       </c>
       <c r="D1927" t="s">
         <v>8</v>
@@ -45380,7 +45383,7 @@
         <v>2970</v>
       </c>
       <c r="C1928" t="s">
-        <v>966</v>
+        <v>1624</v>
       </c>
       <c r="D1928" t="s">
         <v>8</v>
@@ -45397,7 +45400,7 @@
         <v>2970</v>
       </c>
       <c r="C1929" t="s">
-        <v>1581</v>
+        <v>1631</v>
       </c>
       <c r="D1929" t="s">
         <v>8</v>
@@ -45414,7 +45417,7 @@
         <v>2970</v>
       </c>
       <c r="C1930" t="s">
-        <v>1178</v>
+        <v>1598</v>
       </c>
       <c r="D1930" t="s">
         <v>8</v>
@@ -45431,7 +45434,7 @@
         <v>2970</v>
       </c>
       <c r="C1931" t="s">
-        <v>1608</v>
+        <v>1632</v>
       </c>
       <c r="D1931" t="s">
         <v>8</v>
@@ -45442,784 +45445,784 @@
     </row>
     <row r="1932">
       <c r="A1932" t="s">
-        <v>3003</v>
+        <v>3027</v>
       </c>
       <c r="B1932" t="s">
-        <v>2970</v>
+        <v>1287</v>
       </c>
       <c r="C1932" t="s">
-        <v>1619</v>
+        <v>3028</v>
       </c>
       <c r="D1932" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1932" t="s">
-        <v>3021</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="1933">
       <c r="A1933" t="s">
-        <v>3003</v>
+        <v>3030</v>
       </c>
       <c r="B1933" t="s">
-        <v>2970</v>
+        <v>3028</v>
       </c>
       <c r="C1933" t="s">
-        <v>1624</v>
+        <v>225</v>
       </c>
       <c r="D1933" t="s">
         <v>8</v>
       </c>
       <c r="E1933" t="s">
-        <v>3021</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="1934">
       <c r="A1934" t="s">
-        <v>3003</v>
+        <v>3032</v>
       </c>
       <c r="B1934" t="s">
-        <v>2970</v>
+        <v>368</v>
       </c>
       <c r="C1934" t="s">
-        <v>1631</v>
+        <v>3033</v>
       </c>
       <c r="D1934" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1934" t="s">
-        <v>3021</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="1935">
       <c r="A1935" t="s">
-        <v>3003</v>
+        <v>3035</v>
       </c>
       <c r="B1935" t="s">
-        <v>2970</v>
+        <v>443</v>
       </c>
       <c r="C1935" t="s">
-        <v>1598</v>
+        <v>3036</v>
       </c>
       <c r="D1935" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1935" t="s">
-        <v>3021</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="1936">
       <c r="A1936" t="s">
-        <v>3003</v>
+        <v>3038</v>
       </c>
       <c r="B1936" t="s">
-        <v>2970</v>
+        <v>444</v>
       </c>
       <c r="C1936" t="s">
-        <v>1632</v>
+        <v>3039</v>
       </c>
       <c r="D1936" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1936" t="s">
-        <v>3021</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="1937">
       <c r="A1937" t="s">
-        <v>3027</v>
+        <v>3041</v>
       </c>
       <c r="B1937" t="s">
-        <v>1287</v>
+        <v>445</v>
       </c>
       <c r="C1937" t="s">
-        <v>3028</v>
+        <v>3042</v>
       </c>
       <c r="D1937" t="s">
         <v>13</v>
       </c>
       <c r="E1937" t="s">
-        <v>3029</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="1938">
       <c r="A1938" t="s">
-        <v>3030</v>
+        <v>3044</v>
       </c>
       <c r="B1938" t="s">
-        <v>3028</v>
+        <v>3042</v>
       </c>
       <c r="C1938" t="s">
-        <v>225</v>
+        <v>875</v>
       </c>
       <c r="D1938" t="s">
         <v>8</v>
       </c>
       <c r="E1938" t="s">
-        <v>3031</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="1939">
       <c r="A1939" t="s">
-        <v>3032</v>
+        <v>3044</v>
       </c>
       <c r="B1939" t="s">
-        <v>368</v>
+        <v>3042</v>
       </c>
       <c r="C1939" t="s">
-        <v>3033</v>
+        <v>677</v>
       </c>
       <c r="D1939" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E1939" t="s">
-        <v>3034</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="1940">
       <c r="A1940" t="s">
-        <v>3035</v>
+        <v>3044</v>
       </c>
       <c r="B1940" t="s">
-        <v>443</v>
+        <v>3042</v>
       </c>
       <c r="C1940" t="s">
-        <v>3036</v>
+        <v>1467</v>
       </c>
       <c r="D1940" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1940" t="s">
-        <v>3037</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="1941">
       <c r="A1941" t="s">
-        <v>3038</v>
+        <v>3047</v>
       </c>
       <c r="B1941" t="s">
-        <v>444</v>
+        <v>369</v>
       </c>
       <c r="C1941" t="s">
-        <v>3039</v>
+        <v>3048</v>
       </c>
       <c r="D1941" t="s">
         <v>13</v>
       </c>
       <c r="E1941" t="s">
-        <v>3040</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="1942">
       <c r="A1942" t="s">
-        <v>3041</v>
+        <v>3050</v>
       </c>
       <c r="B1942" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C1942" t="s">
-        <v>3042</v>
+        <v>3051</v>
       </c>
       <c r="D1942" t="s">
         <v>13</v>
       </c>
       <c r="E1942" t="s">
-        <v>3043</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="1943">
       <c r="A1943" t="s">
-        <v>3044</v>
+        <v>3053</v>
       </c>
       <c r="B1943" t="s">
-        <v>3042</v>
+        <v>697</v>
       </c>
       <c r="C1943" t="s">
-        <v>875</v>
+        <v>3054</v>
       </c>
       <c r="D1943" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1943" t="s">
-        <v>3045</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="1944">
       <c r="A1944" t="s">
-        <v>3044</v>
+        <v>3056</v>
       </c>
       <c r="B1944" t="s">
-        <v>3042</v>
+        <v>447</v>
       </c>
       <c r="C1944" t="s">
-        <v>677</v>
+        <v>3057</v>
       </c>
       <c r="D1944" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E1944" t="s">
-        <v>3046</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="1945">
       <c r="A1945" t="s">
-        <v>3044</v>
+        <v>3059</v>
       </c>
       <c r="B1945" t="s">
-        <v>3042</v>
+        <v>3026</v>
       </c>
       <c r="C1945" t="s">
-        <v>1467</v>
+        <v>3060</v>
       </c>
       <c r="D1945" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1945" t="s">
-        <v>3045</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="1946">
       <c r="A1946" t="s">
-        <v>3047</v>
+        <v>3062</v>
       </c>
       <c r="B1946" t="s">
-        <v>369</v>
+        <v>719</v>
       </c>
       <c r="C1946" t="s">
-        <v>3048</v>
+        <v>476</v>
       </c>
       <c r="D1946" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1946" t="s">
-        <v>3049</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="1947">
       <c r="A1947" t="s">
-        <v>3050</v>
+        <v>3062</v>
       </c>
       <c r="B1947" t="s">
-        <v>446</v>
+        <v>719</v>
       </c>
       <c r="C1947" t="s">
-        <v>3051</v>
+        <v>2969</v>
       </c>
       <c r="D1947" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1947" t="s">
-        <v>3052</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="1948">
       <c r="A1948" t="s">
-        <v>3053</v>
+        <v>3062</v>
       </c>
       <c r="B1948" t="s">
-        <v>697</v>
+        <v>719</v>
       </c>
       <c r="C1948" t="s">
-        <v>3054</v>
+        <v>478</v>
       </c>
       <c r="D1948" t="s">
         <v>13</v>
       </c>
       <c r="E1948" t="s">
-        <v>3055</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="1949">
       <c r="A1949" t="s">
-        <v>3056</v>
+        <v>3064</v>
       </c>
       <c r="B1949" t="s">
-        <v>447</v>
+        <v>3065</v>
       </c>
       <c r="C1949" t="s">
-        <v>3057</v>
+        <v>347</v>
       </c>
       <c r="D1949" t="s">
         <v>13</v>
       </c>
       <c r="E1949" t="s">
-        <v>3058</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="1950">
       <c r="A1950" t="s">
-        <v>3059</v>
+        <v>3067</v>
       </c>
       <c r="B1950" t="s">
-        <v>3026</v>
+        <v>64</v>
       </c>
       <c r="C1950" t="s">
-        <v>3060</v>
+        <v>405</v>
       </c>
       <c r="D1950" t="s">
         <v>13</v>
       </c>
       <c r="E1950" t="s">
-        <v>3061</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="1951">
       <c r="A1951" t="s">
-        <v>3062</v>
+        <v>3069</v>
       </c>
       <c r="B1951" t="s">
-        <v>719</v>
+        <v>866</v>
       </c>
       <c r="C1951" t="s">
-        <v>476</v>
+        <v>681</v>
       </c>
       <c r="D1951" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1951" t="s">
-        <v>3063</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="1952">
       <c r="A1952" t="s">
-        <v>3062</v>
+        <v>3069</v>
       </c>
       <c r="B1952" t="s">
-        <v>719</v>
+        <v>866</v>
       </c>
       <c r="C1952" t="s">
-        <v>2969</v>
+        <v>35</v>
       </c>
       <c r="D1952" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1952" t="s">
-        <v>3063</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="1953">
       <c r="A1953" t="s">
-        <v>3062</v>
+        <v>3072</v>
       </c>
       <c r="B1953" t="s">
-        <v>719</v>
+        <v>647</v>
       </c>
       <c r="C1953" t="s">
-        <v>478</v>
+        <v>1144</v>
       </c>
       <c r="D1953" t="s">
         <v>13</v>
       </c>
       <c r="E1953" t="s">
-        <v>3063</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="1954">
       <c r="A1954" t="s">
-        <v>3064</v>
+        <v>3074</v>
       </c>
       <c r="B1954" t="s">
-        <v>3065</v>
+        <v>1216</v>
       </c>
       <c r="C1954" t="s">
-        <v>347</v>
+        <v>1144</v>
       </c>
       <c r="D1954" t="s">
         <v>13</v>
       </c>
       <c r="E1954" t="s">
-        <v>3066</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="1955">
       <c r="A1955" t="s">
-        <v>3067</v>
+        <v>3076</v>
       </c>
       <c r="B1955" t="s">
-        <v>64</v>
+        <v>1316</v>
       </c>
       <c r="C1955" t="s">
-        <v>405</v>
+        <v>1144</v>
       </c>
       <c r="D1955" t="s">
         <v>13</v>
       </c>
       <c r="E1955" t="s">
-        <v>3068</v>
+        <v>3077</v>
       </c>
     </row>
     <row r="1956">
       <c r="A1956" t="s">
-        <v>3069</v>
+        <v>3078</v>
       </c>
       <c r="B1956" t="s">
-        <v>866</v>
+        <v>175</v>
       </c>
       <c r="C1956" t="s">
-        <v>681</v>
+        <v>1424</v>
       </c>
       <c r="D1956" t="s">
         <v>13</v>
       </c>
       <c r="E1956" t="s">
-        <v>3070</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="1957">
       <c r="A1957" t="s">
-        <v>3069</v>
+        <v>3080</v>
       </c>
       <c r="B1957" t="s">
-        <v>866</v>
+        <v>175</v>
       </c>
       <c r="C1957" t="s">
-        <v>35</v>
+        <v>1424</v>
       </c>
       <c r="D1957" t="s">
         <v>13</v>
       </c>
       <c r="E1957" t="s">
-        <v>3071</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="1958">
       <c r="A1958" t="s">
-        <v>3072</v>
+        <v>3082</v>
       </c>
       <c r="B1958" t="s">
-        <v>647</v>
+        <v>3083</v>
       </c>
       <c r="C1958" t="s">
-        <v>1144</v>
+        <v>121</v>
       </c>
       <c r="D1958" t="s">
         <v>13</v>
       </c>
       <c r="E1958" t="s">
-        <v>3073</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="1959">
       <c r="A1959" t="s">
-        <v>3074</v>
+        <v>3085</v>
       </c>
       <c r="B1959" t="s">
-        <v>1216</v>
+        <v>3086</v>
       </c>
       <c r="C1959" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="D1959" t="s">
         <v>13</v>
       </c>
       <c r="E1959" t="s">
-        <v>3075</v>
+        <v>3087</v>
       </c>
     </row>
     <row r="1960">
       <c r="A1960" t="s">
-        <v>3076</v>
+        <v>3088</v>
       </c>
       <c r="B1960" t="s">
-        <v>1316</v>
+        <v>798</v>
       </c>
       <c r="C1960" t="s">
-        <v>1144</v>
+        <v>3089</v>
       </c>
       <c r="D1960" t="s">
         <v>13</v>
       </c>
       <c r="E1960" t="s">
-        <v>3077</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="1961">
       <c r="A1961" t="s">
-        <v>3078</v>
+        <v>3091</v>
       </c>
       <c r="B1961" t="s">
-        <v>175</v>
+        <v>269</v>
       </c>
       <c r="C1961" t="s">
-        <v>1424</v>
+        <v>1146</v>
       </c>
       <c r="D1961" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1961" t="s">
-        <v>3079</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="1962">
       <c r="A1962" t="s">
-        <v>3080</v>
+        <v>3091</v>
       </c>
       <c r="B1962" t="s">
-        <v>175</v>
+        <v>269</v>
       </c>
       <c r="C1962" t="s">
-        <v>1424</v>
+        <v>2037</v>
       </c>
       <c r="D1962" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1962" t="s">
-        <v>3081</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="1963">
       <c r="A1963" t="s">
-        <v>3082</v>
+        <v>3093</v>
       </c>
       <c r="B1963" t="s">
-        <v>3083</v>
+        <v>2037</v>
       </c>
       <c r="C1963" t="s">
-        <v>121</v>
+        <v>3094</v>
       </c>
       <c r="D1963" t="s">
         <v>13</v>
       </c>
       <c r="E1963" t="s">
-        <v>3084</v>
+        <v>3095</v>
       </c>
     </row>
     <row r="1964">
       <c r="A1964" t="s">
-        <v>3085</v>
+        <v>3096</v>
       </c>
       <c r="B1964" t="s">
-        <v>3086</v>
+        <v>3097</v>
       </c>
       <c r="C1964" t="s">
-        <v>1146</v>
+        <v>706</v>
       </c>
       <c r="D1964" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E1964" t="s">
-        <v>3087</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="1965">
       <c r="A1965" t="s">
-        <v>3088</v>
+        <v>3099</v>
       </c>
       <c r="B1965" t="s">
-        <v>798</v>
+        <v>2371</v>
       </c>
       <c r="C1965" t="s">
-        <v>3089</v>
+        <v>3100</v>
       </c>
       <c r="D1965" t="s">
         <v>13</v>
       </c>
       <c r="E1965" t="s">
-        <v>3090</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="1966">
       <c r="A1966" t="s">
-        <v>3091</v>
+        <v>3102</v>
       </c>
       <c r="B1966" t="s">
-        <v>269</v>
+        <v>2423</v>
       </c>
       <c r="C1966" t="s">
-        <v>1146</v>
+        <v>3103</v>
       </c>
       <c r="D1966" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1966" t="s">
-        <v>3092</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="1967">
       <c r="A1967" t="s">
-        <v>3091</v>
+        <v>1946</v>
       </c>
       <c r="B1967" t="s">
-        <v>269</v>
+        <v>1946</v>
       </c>
       <c r="C1967" t="s">
-        <v>2037</v>
+        <v>648</v>
       </c>
       <c r="D1967" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E1967" t="s">
-        <v>3092</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="1968">
       <c r="A1968" t="s">
-        <v>3093</v>
+        <v>3106</v>
       </c>
       <c r="B1968" t="s">
-        <v>2037</v>
+        <v>3103</v>
       </c>
       <c r="C1968" t="s">
-        <v>3094</v>
+        <v>648</v>
       </c>
       <c r="D1968" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1968" t="s">
-        <v>3095</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="1969">
       <c r="A1969" t="s">
-        <v>3096</v>
+        <v>3106</v>
       </c>
       <c r="B1969" t="s">
-        <v>3097</v>
+        <v>3103</v>
       </c>
       <c r="C1969" t="s">
-        <v>706</v>
+        <v>3107</v>
       </c>
       <c r="D1969" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1969" t="s">
-        <v>3098</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="1970">
       <c r="A1970" t="s">
-        <v>3099</v>
+        <v>3108</v>
       </c>
       <c r="B1970" t="s">
-        <v>2371</v>
+        <v>3107</v>
       </c>
       <c r="C1970" t="s">
-        <v>3100</v>
+        <v>3109</v>
       </c>
       <c r="D1970" t="s">
         <v>13</v>
       </c>
       <c r="E1970" t="s">
-        <v>3101</v>
+        <v>3110</v>
       </c>
     </row>
     <row r="1971">
       <c r="A1971" t="s">
-        <v>3102</v>
+        <v>2078</v>
       </c>
       <c r="B1971" t="s">
-        <v>2423</v>
+        <v>2078</v>
       </c>
       <c r="C1971" t="s">
-        <v>3103</v>
+        <v>648</v>
       </c>
       <c r="D1971" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E1971" t="s">
-        <v>3104</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="1972">
       <c r="A1972" t="s">
-        <v>1946</v>
+        <v>3112</v>
       </c>
       <c r="B1972" t="s">
-        <v>1946</v>
+        <v>222</v>
       </c>
       <c r="C1972" t="s">
-        <v>648</v>
+        <v>2078</v>
       </c>
       <c r="D1972" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1972" t="s">
-        <v>3105</v>
+        <v>3113</v>
       </c>
     </row>
     <row r="1973">
       <c r="A1973" t="s">
-        <v>3106</v>
+        <v>3114</v>
       </c>
       <c r="B1973" t="s">
-        <v>3103</v>
+        <v>3094</v>
       </c>
       <c r="C1973" t="s">
-        <v>648</v>
+        <v>1942</v>
       </c>
       <c r="D1973" t="s">
         <v>8</v>
       </c>
       <c r="E1973" t="s">
-        <v>2422</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="1974">
       <c r="A1974" t="s">
-        <v>3106</v>
+        <v>3114</v>
       </c>
       <c r="B1974" t="s">
-        <v>3103</v>
+        <v>3094</v>
       </c>
       <c r="C1974" t="s">
-        <v>3107</v>
+        <v>706</v>
       </c>
       <c r="D1974" t="s">
         <v>8</v>
       </c>
       <c r="E1974" t="s">
-        <v>2422</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="1975">
       <c r="A1975" t="s">
-        <v>3108</v>
+        <v>3114</v>
       </c>
       <c r="B1975" t="s">
-        <v>3107</v>
+        <v>3094</v>
       </c>
       <c r="C1975" t="s">
-        <v>3109</v>
+        <v>3117</v>
       </c>
       <c r="D1975" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1975" t="s">
-        <v>3110</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="1976">
       <c r="A1976" t="s">
-        <v>2078</v>
+        <v>3114</v>
       </c>
       <c r="B1976" t="s">
-        <v>2078</v>
+        <v>3094</v>
       </c>
       <c r="C1976" t="s">
-        <v>648</v>
+        <v>796</v>
       </c>
       <c r="D1976" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1976" t="s">
-        <v>3111</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="1977">
       <c r="A1977" t="s">
-        <v>3112</v>
+        <v>3114</v>
       </c>
       <c r="B1977" t="s">
-        <v>222</v>
+        <v>3094</v>
       </c>
       <c r="C1977" t="s">
-        <v>2078</v>
+        <v>2369</v>
       </c>
       <c r="D1977" t="s">
         <v>8</v>
       </c>
       <c r="E1977" t="s">
-        <v>3113</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="1978">
@@ -46230,13 +46233,13 @@
         <v>3094</v>
       </c>
       <c r="C1978" t="s">
-        <v>1942</v>
+        <v>2665</v>
       </c>
       <c r="D1978" t="s">
         <v>8</v>
       </c>
       <c r="E1978" t="s">
-        <v>3115</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="1979">
@@ -46247,13 +46250,13 @@
         <v>3094</v>
       </c>
       <c r="C1979" t="s">
-        <v>706</v>
+        <v>798</v>
       </c>
       <c r="D1979" t="s">
         <v>8</v>
       </c>
       <c r="E1979" t="s">
-        <v>3116</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="1980">
@@ -46264,13 +46267,13 @@
         <v>3094</v>
       </c>
       <c r="C1980" t="s">
-        <v>3117</v>
+        <v>2371</v>
       </c>
       <c r="D1980" t="s">
         <v>8</v>
       </c>
       <c r="E1980" t="s">
-        <v>3115</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="1981">
@@ -46281,13 +46284,13 @@
         <v>3094</v>
       </c>
       <c r="C1981" t="s">
-        <v>796</v>
+        <v>2423</v>
       </c>
       <c r="D1981" t="s">
         <v>8</v>
       </c>
       <c r="E1981" t="s">
-        <v>3118</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="1982">
@@ -46298,13 +46301,13 @@
         <v>3094</v>
       </c>
       <c r="C1982" t="s">
-        <v>2369</v>
+        <v>3120</v>
       </c>
       <c r="D1982" t="s">
         <v>8</v>
       </c>
       <c r="E1982" t="s">
-        <v>3118</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="1983">
@@ -46315,7 +46318,7 @@
         <v>3094</v>
       </c>
       <c r="C1983" t="s">
-        <v>2665</v>
+        <v>2667</v>
       </c>
       <c r="D1983" t="s">
         <v>8</v>
@@ -46332,55 +46335,55 @@
         <v>3094</v>
       </c>
       <c r="C1984" t="s">
-        <v>798</v>
+        <v>3121</v>
       </c>
       <c r="D1984" t="s">
         <v>8</v>
       </c>
       <c r="E1984" t="s">
-        <v>3118</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="1985">
       <c r="A1985" t="s">
-        <v>3114</v>
+        <v>3122</v>
       </c>
       <c r="B1985" t="s">
-        <v>3094</v>
+        <v>1174</v>
       </c>
       <c r="C1985" t="s">
-        <v>2371</v>
+        <v>3123</v>
       </c>
       <c r="D1985" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1985" t="s">
-        <v>3118</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="1986">
       <c r="A1986" t="s">
-        <v>3114</v>
+        <v>3125</v>
       </c>
       <c r="B1986" t="s">
-        <v>3094</v>
+        <v>269</v>
       </c>
       <c r="C1986" t="s">
-        <v>2423</v>
+        <v>706</v>
       </c>
       <c r="D1986" t="s">
         <v>8</v>
       </c>
       <c r="E1986" t="s">
-        <v>3115</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="1987">
       <c r="A1987" t="s">
-        <v>3114</v>
+        <v>3125</v>
       </c>
       <c r="B1987" t="s">
-        <v>3094</v>
+        <v>269</v>
       </c>
       <c r="C1987" t="s">
         <v>3120</v>
@@ -46389,109 +46392,109 @@
         <v>8</v>
       </c>
       <c r="E1987" t="s">
-        <v>3116</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="1988">
       <c r="A1988" t="s">
-        <v>3114</v>
+        <v>3127</v>
       </c>
       <c r="B1988" t="s">
-        <v>3094</v>
+        <v>3120</v>
       </c>
       <c r="C1988" t="s">
-        <v>2667</v>
+        <v>3128</v>
       </c>
       <c r="D1988" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1988" t="s">
-        <v>3119</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="1989">
       <c r="A1989" t="s">
-        <v>3114</v>
+        <v>3130</v>
       </c>
       <c r="B1989" t="s">
-        <v>3094</v>
+        <v>3128</v>
       </c>
       <c r="C1989" t="s">
-        <v>3121</v>
+        <v>648</v>
       </c>
       <c r="D1989" t="s">
         <v>8</v>
       </c>
       <c r="E1989" t="s">
-        <v>3115</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="1990">
       <c r="A1990" t="s">
-        <v>3122</v>
+        <v>3130</v>
       </c>
       <c r="B1990" t="s">
-        <v>1174</v>
+        <v>3128</v>
       </c>
       <c r="C1990" t="s">
-        <v>3123</v>
+        <v>2654</v>
       </c>
       <c r="D1990" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1990" t="s">
-        <v>3124</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="1991">
       <c r="A1991" t="s">
-        <v>3125</v>
+        <v>3130</v>
       </c>
       <c r="B1991" t="s">
-        <v>269</v>
+        <v>3128</v>
       </c>
       <c r="C1991" t="s">
-        <v>706</v>
+        <v>1157</v>
       </c>
       <c r="D1991" t="s">
         <v>8</v>
       </c>
       <c r="E1991" t="s">
-        <v>3126</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="1992">
       <c r="A1992" t="s">
-        <v>3125</v>
+        <v>3130</v>
       </c>
       <c r="B1992" t="s">
-        <v>269</v>
+        <v>3128</v>
       </c>
       <c r="C1992" t="s">
-        <v>3120</v>
+        <v>2829</v>
       </c>
       <c r="D1992" t="s">
         <v>8</v>
       </c>
       <c r="E1992" t="s">
-        <v>3126</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="1993">
       <c r="A1993" t="s">
-        <v>3127</v>
+        <v>3130</v>
       </c>
       <c r="B1993" t="s">
-        <v>3120</v>
+        <v>3128</v>
       </c>
       <c r="C1993" t="s">
-        <v>3128</v>
+        <v>3107</v>
       </c>
       <c r="D1993" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1993" t="s">
-        <v>3129</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="1994">
@@ -46502,7 +46505,7 @@
         <v>3128</v>
       </c>
       <c r="C1994" t="s">
-        <v>648</v>
+        <v>1174</v>
       </c>
       <c r="D1994" t="s">
         <v>8</v>
@@ -46519,13 +46522,13 @@
         <v>3128</v>
       </c>
       <c r="C1995" t="s">
-        <v>2654</v>
+        <v>2833</v>
       </c>
       <c r="D1995" t="s">
         <v>8</v>
       </c>
       <c r="E1995" t="s">
-        <v>3131</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="1996">
@@ -46536,7 +46539,7 @@
         <v>3128</v>
       </c>
       <c r="C1996" t="s">
-        <v>1157</v>
+        <v>3133</v>
       </c>
       <c r="D1996" t="s">
         <v>8</v>
@@ -46547,1650 +46550,1565 @@
     </row>
     <row r="1997">
       <c r="A1997" t="s">
-        <v>3130</v>
+        <v>3134</v>
       </c>
       <c r="B1997" t="s">
-        <v>3128</v>
+        <v>2833</v>
       </c>
       <c r="C1997" t="s">
-        <v>2829</v>
+        <v>3135</v>
       </c>
       <c r="D1997" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1997" t="s">
-        <v>3132</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="1998">
       <c r="A1998" t="s">
-        <v>3130</v>
+        <v>3137</v>
       </c>
       <c r="B1998" t="s">
-        <v>3128</v>
+        <v>2667</v>
       </c>
       <c r="C1998" t="s">
-        <v>3107</v>
+        <v>3138</v>
       </c>
       <c r="D1998" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1998" t="s">
-        <v>3131</v>
+        <v>3139</v>
       </c>
     </row>
     <row r="1999">
       <c r="A1999" t="s">
-        <v>3130</v>
+        <v>3140</v>
       </c>
       <c r="B1999" t="s">
-        <v>3128</v>
+        <v>3121</v>
       </c>
       <c r="C1999" t="s">
-        <v>1174</v>
+        <v>3141</v>
       </c>
       <c r="D1999" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1999" t="s">
-        <v>3131</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="2000">
       <c r="A2000" t="s">
-        <v>3130</v>
+        <v>3143</v>
       </c>
       <c r="B2000" t="s">
-        <v>3128</v>
+        <v>3141</v>
       </c>
       <c r="C2000" t="s">
-        <v>2833</v>
+        <v>1942</v>
       </c>
       <c r="D2000" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2000" t="s">
-        <v>3132</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="2001">
       <c r="A2001" t="s">
-        <v>3130</v>
+        <v>3143</v>
       </c>
       <c r="B2001" t="s">
-        <v>3128</v>
+        <v>3141</v>
       </c>
       <c r="C2001" t="s">
-        <v>3133</v>
+        <v>2654</v>
       </c>
       <c r="D2001" t="s">
         <v>8</v>
       </c>
       <c r="E2001" t="s">
-        <v>3131</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="2002">
       <c r="A2002" t="s">
-        <v>3134</v>
+        <v>3143</v>
       </c>
       <c r="B2002" t="s">
-        <v>2833</v>
+        <v>3141</v>
       </c>
       <c r="C2002" t="s">
-        <v>3135</v>
+        <v>3133</v>
       </c>
       <c r="D2002" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2002" t="s">
-        <v>3136</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="2003">
       <c r="A2003" t="s">
-        <v>3137</v>
+        <v>3145</v>
       </c>
       <c r="B2003" t="s">
-        <v>2667</v>
+        <v>1175</v>
       </c>
       <c r="C2003" t="s">
-        <v>3138</v>
+        <v>3146</v>
       </c>
       <c r="D2003" t="s">
         <v>13</v>
       </c>
       <c r="E2003" t="s">
-        <v>3139</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="2004">
       <c r="A2004" t="s">
-        <v>3140</v>
+        <v>3148</v>
       </c>
       <c r="B2004" t="s">
-        <v>3121</v>
+        <v>3133</v>
       </c>
       <c r="C2004" t="s">
-        <v>3141</v>
+        <v>3149</v>
       </c>
       <c r="D2004" t="s">
         <v>13</v>
       </c>
       <c r="E2004" t="s">
-        <v>3142</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="2005">
       <c r="A2005" t="s">
-        <v>3143</v>
+        <v>3151</v>
       </c>
       <c r="B2005" t="s">
-        <v>3141</v>
+        <v>3149</v>
       </c>
       <c r="C2005" t="s">
-        <v>1942</v>
+        <v>1159</v>
       </c>
       <c r="D2005" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2005" t="s">
-        <v>3144</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="2006">
       <c r="A2006" t="s">
-        <v>3143</v>
+        <v>3151</v>
       </c>
       <c r="B2006" t="s">
-        <v>3141</v>
+        <v>3149</v>
       </c>
       <c r="C2006" t="s">
-        <v>2654</v>
+        <v>2831</v>
       </c>
       <c r="D2006" t="s">
         <v>8</v>
       </c>
       <c r="E2006" t="s">
-        <v>3144</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="2007">
       <c r="A2007" t="s">
-        <v>3143</v>
+        <v>3151</v>
       </c>
       <c r="B2007" t="s">
-        <v>3141</v>
+        <v>3149</v>
       </c>
       <c r="C2007" t="s">
-        <v>3133</v>
+        <v>1175</v>
       </c>
       <c r="D2007" t="s">
         <v>8</v>
       </c>
       <c r="E2007" t="s">
-        <v>3144</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="2008">
       <c r="A2008" t="s">
-        <v>3145</v>
+        <v>3151</v>
       </c>
       <c r="B2008" t="s">
-        <v>1175</v>
+        <v>3149</v>
       </c>
       <c r="C2008" t="s">
-        <v>3146</v>
+        <v>2834</v>
       </c>
       <c r="D2008" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2008" t="s">
-        <v>3147</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="2009">
       <c r="A2009" t="s">
-        <v>3148</v>
+        <v>3153</v>
       </c>
       <c r="B2009" t="s">
-        <v>3133</v>
+        <v>2834</v>
       </c>
       <c r="C2009" t="s">
-        <v>3149</v>
+        <v>3154</v>
       </c>
       <c r="D2009" t="s">
         <v>13</v>
       </c>
       <c r="E2009" t="s">
-        <v>3150</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="2010">
       <c r="A2010" t="s">
-        <v>3151</v>
+        <v>3156</v>
       </c>
       <c r="B2010" t="s">
-        <v>3149</v>
+        <v>3156</v>
       </c>
       <c r="C2010" t="s">
-        <v>1159</v>
+        <v>3117</v>
       </c>
       <c r="D2010" t="s">
         <v>8</v>
       </c>
       <c r="E2010" t="s">
-        <v>3152</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="2011">
       <c r="A2011" t="s">
-        <v>3151</v>
+        <v>3156</v>
       </c>
       <c r="B2011" t="s">
-        <v>3149</v>
+        <v>3156</v>
       </c>
       <c r="C2011" t="s">
-        <v>2831</v>
+        <v>3121</v>
       </c>
       <c r="D2011" t="s">
         <v>8</v>
       </c>
       <c r="E2011" t="s">
-        <v>3152</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="2012">
       <c r="A2012" t="s">
-        <v>3151</v>
+        <v>3158</v>
       </c>
       <c r="B2012" t="s">
-        <v>3149</v>
+        <v>3158</v>
       </c>
       <c r="C2012" t="s">
-        <v>1175</v>
+        <v>1146</v>
       </c>
       <c r="D2012" t="s">
         <v>8</v>
       </c>
       <c r="E2012" t="s">
-        <v>3152</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="2013">
       <c r="A2013" t="s">
-        <v>3151</v>
+        <v>3160</v>
       </c>
       <c r="B2013" t="s">
-        <v>3149</v>
+        <v>3160</v>
       </c>
       <c r="C2013" t="s">
-        <v>2834</v>
+        <v>2499</v>
       </c>
       <c r="D2013" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2013" t="s">
-        <v>3152</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="2014">
       <c r="A2014" t="s">
-        <v>3153</v>
+        <v>3162</v>
       </c>
       <c r="B2014" t="s">
-        <v>2834</v>
+        <v>1820</v>
       </c>
       <c r="C2014" t="s">
-        <v>3154</v>
+        <v>1202</v>
       </c>
       <c r="D2014" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2014" t="s">
-        <v>3155</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="2015">
       <c r="A2015" t="s">
-        <v>3156</v>
+        <v>3162</v>
       </c>
       <c r="B2015" t="s">
-        <v>3156</v>
+        <v>1820</v>
       </c>
       <c r="C2015" t="s">
-        <v>3117</v>
+        <v>1806</v>
       </c>
       <c r="D2015" t="s">
         <v>8</v>
       </c>
       <c r="E2015" t="s">
-        <v>3157</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="2016">
       <c r="A2016" t="s">
-        <v>3156</v>
+        <v>3164</v>
       </c>
       <c r="B2016" t="s">
-        <v>3156</v>
+        <v>64</v>
       </c>
       <c r="C2016" t="s">
-        <v>3121</v>
+        <v>421</v>
       </c>
       <c r="D2016" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2016" t="s">
-        <v>3157</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="2017">
       <c r="A2017" t="s">
-        <v>3158</v>
+        <v>3164</v>
       </c>
       <c r="B2017" t="s">
-        <v>3158</v>
+        <v>64</v>
       </c>
       <c r="C2017" t="s">
-        <v>1146</v>
+        <v>354</v>
       </c>
       <c r="D2017" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2017" t="s">
-        <v>3159</v>
+        <v>3166</v>
       </c>
     </row>
     <row r="2018">
       <c r="A2018" t="s">
-        <v>3160</v>
+        <v>3167</v>
       </c>
       <c r="B2018" t="s">
-        <v>3160</v>
+        <v>3168</v>
       </c>
       <c r="C2018" t="s">
-        <v>2499</v>
+        <v>33</v>
       </c>
       <c r="D2018" t="s">
         <v>13</v>
       </c>
       <c r="E2018" t="s">
-        <v>3161</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="2019">
       <c r="A2019" t="s">
-        <v>3162</v>
+        <v>3170</v>
       </c>
       <c r="B2019" t="s">
-        <v>1820</v>
+        <v>3171</v>
       </c>
       <c r="C2019" t="s">
-        <v>1202</v>
+        <v>33</v>
       </c>
       <c r="D2019" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2019" t="s">
-        <v>3163</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="2020">
       <c r="A2020" t="s">
-        <v>3162</v>
+        <v>3173</v>
       </c>
       <c r="B2020" t="s">
-        <v>1820</v>
+        <v>3174</v>
       </c>
       <c r="C2020" t="s">
-        <v>1806</v>
+        <v>505</v>
       </c>
       <c r="D2020" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2020" t="s">
-        <v>3163</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="2021">
       <c r="A2021" t="s">
-        <v>3164</v>
+        <v>1021</v>
       </c>
       <c r="B2021" t="s">
-        <v>64</v>
+        <v>1021</v>
       </c>
       <c r="C2021" t="s">
-        <v>421</v>
+        <v>113</v>
       </c>
       <c r="D2021" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2021" t="s">
-        <v>3165</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="2022">
       <c r="A2022" t="s">
-        <v>3164</v>
+        <v>1021</v>
       </c>
       <c r="B2022" t="s">
-        <v>64</v>
+        <v>1021</v>
       </c>
       <c r="C2022" t="s">
-        <v>354</v>
+        <v>117</v>
       </c>
       <c r="D2022" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2022" t="s">
-        <v>3166</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="2023">
       <c r="A2023" t="s">
-        <v>3167</v>
+        <v>1021</v>
       </c>
       <c r="B2023" t="s">
-        <v>3168</v>
+        <v>1021</v>
       </c>
       <c r="C2023" t="s">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="D2023" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2023" t="s">
-        <v>3169</v>
+        <v>3177</v>
       </c>
     </row>
     <row r="2024">
       <c r="A2024" t="s">
-        <v>3170</v>
+        <v>1021</v>
       </c>
       <c r="B2024" t="s">
-        <v>3171</v>
+        <v>1021</v>
       </c>
       <c r="C2024" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D2024" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2024" t="s">
-        <v>3172</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="2025">
       <c r="A2025" t="s">
-        <v>3173</v>
+        <v>1021</v>
       </c>
       <c r="B2025" t="s">
-        <v>3174</v>
+        <v>1021</v>
       </c>
       <c r="C2025" t="s">
-        <v>505</v>
+        <v>481</v>
       </c>
       <c r="D2025" t="s">
         <v>13</v>
       </c>
       <c r="E2025" t="s">
-        <v>3175</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="2026">
       <c r="A2026" t="s">
-        <v>1021</v>
+        <v>3178</v>
       </c>
       <c r="B2026" t="s">
-        <v>1021</v>
+        <v>3178</v>
       </c>
       <c r="C2026" t="s">
-        <v>113</v>
+        <v>1698</v>
       </c>
       <c r="D2026" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E2026" t="s">
-        <v>3176</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="2027">
       <c r="A2027" t="s">
+        <v>3178</v>
+      </c>
+      <c r="B2027" t="s">
+        <v>3178</v>
+      </c>
+      <c r="C2027" t="s">
         <v>1021</v>
       </c>
-      <c r="B2027" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C2027" t="s">
-        <v>117</v>
-      </c>
       <c r="D2027" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E2027" t="s">
-        <v>3176</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="2028">
       <c r="A2028" t="s">
+        <v>3180</v>
+      </c>
+      <c r="B2028" t="s">
+        <v>3181</v>
+      </c>
+      <c r="C2028" t="s">
         <v>1021</v>
       </c>
-      <c r="B2028" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C2028" t="s">
-        <v>119</v>
-      </c>
       <c r="D2028" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E2028" t="s">
-        <v>3177</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="2029">
       <c r="A2029" t="s">
-        <v>1021</v>
+        <v>3182</v>
       </c>
       <c r="B2029" t="s">
-        <v>1021</v>
+        <v>3183</v>
       </c>
       <c r="C2029" t="s">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="D2029" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E2029" t="s">
-        <v>3176</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="2030">
       <c r="A2030" t="s">
-        <v>1021</v>
+        <v>3182</v>
       </c>
       <c r="B2030" t="s">
-        <v>1021</v>
+        <v>3183</v>
       </c>
       <c r="C2030" t="s">
-        <v>481</v>
+        <v>16</v>
       </c>
       <c r="D2030" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2030" t="s">
-        <v>3176</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="2031">
       <c r="A2031" t="s">
-        <v>3178</v>
+        <v>3182</v>
       </c>
       <c r="B2031" t="s">
-        <v>3178</v>
+        <v>3183</v>
       </c>
       <c r="C2031" t="s">
-        <v>1698</v>
+        <v>2607</v>
       </c>
       <c r="D2031" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2031" t="s">
-        <v>3179</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="2032">
       <c r="A2032" t="s">
-        <v>3178</v>
+        <v>3182</v>
       </c>
       <c r="B2032" t="s">
-        <v>3178</v>
+        <v>3183</v>
       </c>
       <c r="C2032" t="s">
-        <v>1021</v>
+        <v>1170</v>
       </c>
       <c r="D2032" t="s">
         <v>8</v>
       </c>
       <c r="E2032" t="s">
-        <v>3179</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="2033">
       <c r="A2033" t="s">
-        <v>3180</v>
+        <v>3182</v>
       </c>
       <c r="B2033" t="s">
-        <v>3181</v>
+        <v>3183</v>
       </c>
       <c r="C2033" t="s">
-        <v>1021</v>
+        <v>642</v>
       </c>
       <c r="D2033" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2033" t="s">
-        <v>1702</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="2034">
       <c r="A2034" t="s">
-        <v>3182</v>
+        <v>3187</v>
       </c>
       <c r="B2034" t="s">
-        <v>3183</v>
+        <v>64</v>
       </c>
       <c r="C2034" t="s">
-        <v>53</v>
+        <v>172</v>
       </c>
       <c r="D2034" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2034" t="s">
-        <v>3184</v>
+        <v>3188</v>
       </c>
     </row>
     <row r="2035">
       <c r="A2035" t="s">
-        <v>3182</v>
+        <v>3189</v>
       </c>
       <c r="B2035" t="s">
-        <v>3183</v>
+        <v>335</v>
       </c>
       <c r="C2035" t="s">
-        <v>16</v>
+        <v>225</v>
       </c>
       <c r="D2035" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2035" t="s">
-        <v>3185</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="2036">
       <c r="A2036" t="s">
-        <v>3182</v>
+        <v>3191</v>
       </c>
       <c r="B2036" t="s">
-        <v>3183</v>
+        <v>64</v>
       </c>
       <c r="C2036" t="s">
-        <v>2607</v>
+        <v>1021</v>
       </c>
       <c r="D2036" t="s">
         <v>13</v>
       </c>
       <c r="E2036" t="s">
-        <v>3184</v>
+        <v>3192</v>
       </c>
     </row>
     <row r="2037">
       <c r="A2037" t="s">
-        <v>3182</v>
+        <v>3193</v>
       </c>
       <c r="B2037" t="s">
-        <v>3183</v>
+        <v>3193</v>
       </c>
       <c r="C2037" t="s">
-        <v>1170</v>
+        <v>1946</v>
       </c>
       <c r="D2037" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2037" t="s">
-        <v>3185</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="2038">
       <c r="A2038" t="s">
-        <v>3182</v>
+        <v>3193</v>
       </c>
       <c r="B2038" t="s">
-        <v>3183</v>
+        <v>3193</v>
       </c>
       <c r="C2038" t="s">
-        <v>642</v>
+        <v>2078</v>
       </c>
       <c r="D2038" t="s">
         <v>13</v>
       </c>
       <c r="E2038" t="s">
-        <v>3186</v>
+        <v>3195</v>
       </c>
     </row>
     <row r="2039">
       <c r="A2039" t="s">
-        <v>3187</v>
+        <v>3196</v>
       </c>
       <c r="B2039" t="s">
-        <v>64</v>
+        <v>3196</v>
       </c>
       <c r="C2039" t="s">
-        <v>172</v>
+        <v>2081</v>
       </c>
       <c r="D2039" t="s">
         <v>13</v>
       </c>
       <c r="E2039" t="s">
-        <v>3188</v>
+        <v>3197</v>
       </c>
     </row>
     <row r="2040">
       <c r="A2040" t="s">
-        <v>3189</v>
+        <v>3198</v>
       </c>
       <c r="B2040" t="s">
-        <v>335</v>
+        <v>1375</v>
       </c>
       <c r="C2040" t="s">
-        <v>225</v>
+        <v>285</v>
       </c>
       <c r="D2040" t="s">
         <v>13</v>
       </c>
       <c r="E2040" t="s">
-        <v>3190</v>
+        <v>3199</v>
       </c>
     </row>
     <row r="2041">
       <c r="A2041" t="s">
-        <v>3191</v>
+        <v>3200</v>
       </c>
       <c r="B2041" t="s">
-        <v>64</v>
+        <v>206</v>
       </c>
       <c r="C2041" t="s">
-        <v>1021</v>
+        <v>347</v>
       </c>
       <c r="D2041" t="s">
         <v>13</v>
       </c>
       <c r="E2041" t="s">
-        <v>3192</v>
+        <v>3201</v>
       </c>
     </row>
     <row r="2042">
       <c r="A2042" t="s">
-        <v>3193</v>
+        <v>3202</v>
       </c>
       <c r="B2042" t="s">
-        <v>3193</v>
+        <v>1375</v>
       </c>
       <c r="C2042" t="s">
-        <v>1946</v>
+        <v>103</v>
       </c>
       <c r="D2042" t="s">
         <v>13</v>
       </c>
       <c r="E2042" t="s">
-        <v>3194</v>
+        <v>3203</v>
       </c>
     </row>
     <row r="2043">
       <c r="A2043" t="s">
-        <v>3193</v>
+        <v>3204</v>
       </c>
       <c r="B2043" t="s">
-        <v>3193</v>
+        <v>1310</v>
       </c>
       <c r="C2043" t="s">
-        <v>2078</v>
+        <v>29</v>
       </c>
       <c r="D2043" t="s">
         <v>13</v>
       </c>
       <c r="E2043" t="s">
-        <v>3195</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="2044">
       <c r="A2044" t="s">
-        <v>3196</v>
+        <v>3206</v>
       </c>
       <c r="B2044" t="s">
-        <v>3196</v>
+        <v>3206</v>
       </c>
       <c r="C2044" t="s">
-        <v>2081</v>
+        <v>890</v>
       </c>
       <c r="D2044" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2044" t="s">
-        <v>3197</v>
+        <v>3207</v>
       </c>
     </row>
     <row r="2045">
       <c r="A2045" t="s">
-        <v>3198</v>
+        <v>3206</v>
       </c>
       <c r="B2045" t="s">
-        <v>1375</v>
+        <v>3208</v>
       </c>
       <c r="C2045" t="s">
-        <v>285</v>
+        <v>373</v>
       </c>
       <c r="D2045" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2045" t="s">
-        <v>3199</v>
+        <v>732</v>
       </c>
     </row>
     <row r="2046">
       <c r="A2046" t="s">
-        <v>3200</v>
+        <v>3209</v>
       </c>
       <c r="B2046" t="s">
-        <v>206</v>
+        <v>3210</v>
       </c>
       <c r="C2046" t="s">
-        <v>347</v>
+        <v>3211</v>
       </c>
       <c r="D2046" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2046" t="s">
-        <v>3201</v>
+        <v>3212</v>
       </c>
     </row>
     <row r="2047">
       <c r="A2047" t="s">
-        <v>3202</v>
+        <v>2265</v>
       </c>
       <c r="B2047" t="s">
-        <v>1375</v>
+        <v>2265</v>
       </c>
       <c r="C2047" t="s">
-        <v>103</v>
+        <v>3211</v>
       </c>
       <c r="D2047" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2047" t="s">
-        <v>3203</v>
+        <v>3213</v>
       </c>
     </row>
     <row r="2048">
       <c r="A2048" t="s">
-        <v>3204</v>
+        <v>2265</v>
       </c>
       <c r="B2048" t="s">
-        <v>1310</v>
+        <v>3214</v>
       </c>
       <c r="C2048" t="s">
-        <v>29</v>
+        <v>2265</v>
       </c>
       <c r="D2048" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2048" t="s">
-        <v>3205</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="2049">
       <c r="A2049" t="s">
-        <v>3206</v>
+        <v>3216</v>
       </c>
       <c r="B2049" t="s">
-        <v>3206</v>
+        <v>3217</v>
       </c>
       <c r="C2049" t="s">
-        <v>890</v>
+        <v>159</v>
       </c>
       <c r="D2049" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2049" t="s">
-        <v>3207</v>
+        <v>3218</v>
       </c>
     </row>
     <row r="2050">
       <c r="A2050" t="s">
-        <v>3206</v>
+        <v>3219</v>
       </c>
       <c r="B2050" t="s">
-        <v>3208</v>
+        <v>3219</v>
       </c>
       <c r="C2050" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="D2050" t="s">
         <v>8</v>
       </c>
       <c r="E2050" t="s">
-        <v>732</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="2051">
       <c r="A2051" t="s">
-        <v>3209</v>
+        <v>3219</v>
       </c>
       <c r="B2051" t="s">
-        <v>3210</v>
+        <v>3219</v>
       </c>
       <c r="C2051" t="s">
-        <v>3211</v>
+        <v>401</v>
       </c>
       <c r="D2051" t="s">
         <v>8</v>
       </c>
       <c r="E2051" t="s">
-        <v>3212</v>
+        <v>3221</v>
       </c>
     </row>
     <row r="2052">
       <c r="A2052" t="s">
-        <v>2265</v>
+        <v>3219</v>
       </c>
       <c r="B2052" t="s">
-        <v>2265</v>
+        <v>3219</v>
       </c>
       <c r="C2052" t="s">
-        <v>3211</v>
+        <v>53</v>
       </c>
       <c r="D2052" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E2052" t="s">
-        <v>3213</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="2053">
       <c r="A2053" t="s">
-        <v>2265</v>
+        <v>3223</v>
       </c>
       <c r="B2053" t="s">
-        <v>3214</v>
+        <v>3223</v>
       </c>
       <c r="C2053" t="s">
-        <v>2265</v>
+        <v>162</v>
       </c>
       <c r="D2053" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2053" t="s">
-        <v>3215</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="2054">
       <c r="A2054" t="s">
-        <v>3216</v>
+        <v>3225</v>
       </c>
       <c r="B2054" t="s">
-        <v>3217</v>
+        <v>222</v>
       </c>
       <c r="C2054" t="s">
-        <v>159</v>
+        <v>575</v>
       </c>
       <c r="D2054" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2054" t="s">
-        <v>3218</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="2055">
       <c r="A2055" t="s">
-        <v>3219</v>
+        <v>3227</v>
       </c>
       <c r="B2055" t="s">
-        <v>3219</v>
+        <v>357</v>
       </c>
       <c r="C2055" t="s">
-        <v>399</v>
+        <v>841</v>
       </c>
       <c r="D2055" t="s">
         <v>8</v>
       </c>
       <c r="E2055" t="s">
-        <v>3220</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="2056">
       <c r="A2056" t="s">
-        <v>3219</v>
+        <v>3229</v>
       </c>
       <c r="B2056" t="s">
-        <v>3219</v>
+        <v>211</v>
       </c>
       <c r="C2056" t="s">
-        <v>401</v>
+        <v>693</v>
       </c>
       <c r="D2056" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2056" t="s">
-        <v>3221</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="2057">
       <c r="A2057" t="s">
-        <v>3219</v>
+        <v>3231</v>
       </c>
       <c r="B2057" t="s">
-        <v>3219</v>
+        <v>211</v>
       </c>
       <c r="C2057" t="s">
-        <v>53</v>
+        <v>693</v>
       </c>
       <c r="D2057" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2057" t="s">
-        <v>3222</v>
+        <v>3232</v>
       </c>
     </row>
     <row r="2058">
       <c r="A2058" t="s">
-        <v>3223</v>
+        <v>3233</v>
       </c>
       <c r="B2058" t="s">
-        <v>3223</v>
+        <v>335</v>
       </c>
       <c r="C2058" t="s">
-        <v>162</v>
+        <v>2753</v>
       </c>
       <c r="D2058" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2058" t="s">
-        <v>3224</v>
+        <v>3234</v>
       </c>
     </row>
     <row r="2059">
       <c r="A2059" t="s">
-        <v>3225</v>
+        <v>3233</v>
       </c>
       <c r="B2059" t="s">
-        <v>222</v>
+        <v>335</v>
       </c>
       <c r="C2059" t="s">
-        <v>575</v>
+        <v>3026</v>
       </c>
       <c r="D2059" t="s">
         <v>8</v>
       </c>
       <c r="E2059" t="s">
-        <v>3226</v>
+        <v>3234</v>
       </c>
     </row>
     <row r="2060">
       <c r="A2060" t="s">
-        <v>3227</v>
+        <v>3235</v>
       </c>
       <c r="B2060" t="s">
-        <v>357</v>
+        <v>3236</v>
       </c>
       <c r="C2060" t="s">
-        <v>841</v>
+        <v>2753</v>
       </c>
       <c r="D2060" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2060" t="s">
-        <v>3228</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="2061">
       <c r="A2061" t="s">
-        <v>3229</v>
+        <v>3238</v>
       </c>
       <c r="B2061" t="s">
-        <v>211</v>
+        <v>3239</v>
       </c>
       <c r="C2061" t="s">
-        <v>693</v>
+        <v>2753</v>
       </c>
       <c r="D2061" t="s">
         <v>13</v>
       </c>
       <c r="E2061" t="s">
-        <v>3230</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="2062">
       <c r="A2062" t="s">
-        <v>3231</v>
+        <v>3241</v>
       </c>
       <c r="B2062" t="s">
-        <v>211</v>
+        <v>3242</v>
       </c>
       <c r="C2062" t="s">
-        <v>693</v>
+        <v>492</v>
       </c>
       <c r="D2062" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2062" t="s">
-        <v>3232</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="2063">
       <c r="A2063" t="s">
-        <v>3233</v>
+        <v>3244</v>
       </c>
       <c r="B2063" t="s">
-        <v>335</v>
+        <v>3245</v>
       </c>
       <c r="C2063" t="s">
-        <v>2753</v>
+        <v>492</v>
       </c>
       <c r="D2063" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E2063" t="s">
-        <v>3234</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="2064">
       <c r="A2064" t="s">
-        <v>3233</v>
+        <v>3247</v>
       </c>
       <c r="B2064" t="s">
-        <v>335</v>
+        <v>3248</v>
       </c>
       <c r="C2064" t="s">
-        <v>3026</v>
+        <v>117</v>
       </c>
       <c r="D2064" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E2064" t="s">
-        <v>3234</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="2065">
       <c r="A2065" t="s">
-        <v>3235</v>
+        <v>3247</v>
       </c>
       <c r="B2065" t="s">
-        <v>3236</v>
+        <v>3248</v>
       </c>
       <c r="C2065" t="s">
-        <v>2753</v>
+        <v>121</v>
       </c>
       <c r="D2065" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2065" t="s">
-        <v>3237</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="2066">
       <c r="A2066" t="s">
-        <v>3238</v>
+        <v>291</v>
       </c>
       <c r="B2066" t="s">
-        <v>3239</v>
+        <v>291</v>
       </c>
       <c r="C2066" t="s">
-        <v>2753</v>
+        <v>35</v>
       </c>
       <c r="D2066" t="s">
         <v>13</v>
       </c>
       <c r="E2066" t="s">
-        <v>3240</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="2067">
       <c r="A2067" t="s">
-        <v>3241</v>
+        <v>291</v>
       </c>
       <c r="B2067" t="s">
-        <v>3242</v>
+        <v>291</v>
       </c>
       <c r="C2067" t="s">
-        <v>492</v>
+        <v>373</v>
       </c>
       <c r="D2067" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2067" t="s">
-        <v>3243</v>
+        <v>3252</v>
       </c>
     </row>
     <row r="2068">
       <c r="A2068" t="s">
-        <v>3244</v>
+        <v>291</v>
       </c>
       <c r="B2068" t="s">
-        <v>3245</v>
+        <v>291</v>
       </c>
       <c r="C2068" t="s">
-        <v>492</v>
+        <v>911</v>
       </c>
       <c r="D2068" t="s">
         <v>17</v>
       </c>
       <c r="E2068" t="s">
-        <v>3246</v>
+        <v>3253</v>
       </c>
     </row>
     <row r="2069">
       <c r="A2069" t="s">
-        <v>3247</v>
+        <v>3254</v>
       </c>
       <c r="B2069" t="s">
-        <v>3248</v>
+        <v>211</v>
       </c>
       <c r="C2069" t="s">
-        <v>117</v>
+        <v>735</v>
       </c>
       <c r="D2069" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2069" t="s">
-        <v>3249</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="2070">
       <c r="A2070" t="s">
-        <v>3247</v>
+        <v>3256</v>
       </c>
       <c r="B2070" t="s">
-        <v>3248</v>
+        <v>211</v>
       </c>
       <c r="C2070" t="s">
-        <v>121</v>
+        <v>735</v>
       </c>
       <c r="D2070" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2070" t="s">
-        <v>3250</v>
+        <v>3257</v>
       </c>
     </row>
     <row r="2071">
       <c r="A2071" t="s">
-        <v>291</v>
+        <v>3258</v>
       </c>
       <c r="B2071" t="s">
-        <v>291</v>
+        <v>211</v>
       </c>
       <c r="C2071" t="s">
-        <v>35</v>
+        <v>735</v>
       </c>
       <c r="D2071" t="s">
         <v>13</v>
       </c>
       <c r="E2071" t="s">
-        <v>3251</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="2072">
       <c r="A2072" t="s">
-        <v>291</v>
+        <v>3260</v>
       </c>
       <c r="B2072" t="s">
         <v>291</v>
       </c>
       <c r="C2072" t="s">
-        <v>373</v>
+        <v>103</v>
       </c>
       <c r="D2072" t="s">
         <v>13</v>
       </c>
       <c r="E2072" t="s">
-        <v>3252</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="2073">
       <c r="A2073" t="s">
-        <v>291</v>
+        <v>3262</v>
       </c>
       <c r="B2073" t="s">
-        <v>291</v>
+        <v>3262</v>
       </c>
       <c r="C2073" t="s">
-        <v>911</v>
+        <v>1935</v>
       </c>
       <c r="D2073" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E2073" t="s">
-        <v>3253</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="2074">
       <c r="A2074" t="s">
-        <v>3254</v>
+        <v>3262</v>
       </c>
       <c r="B2074" t="s">
-        <v>211</v>
+        <v>3262</v>
       </c>
       <c r="C2074" t="s">
-        <v>735</v>
+        <v>922</v>
       </c>
       <c r="D2074" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2074" t="s">
-        <v>3255</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="2075">
       <c r="A2075" t="s">
-        <v>3256</v>
+        <v>3264</v>
       </c>
       <c r="B2075" t="s">
-        <v>211</v>
+        <v>3265</v>
       </c>
       <c r="C2075" t="s">
-        <v>735</v>
+        <v>373</v>
       </c>
       <c r="D2075" t="s">
         <v>13</v>
       </c>
       <c r="E2075" t="s">
-        <v>3257</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="2076">
       <c r="A2076" t="s">
-        <v>3258</v>
+        <v>3264</v>
       </c>
       <c r="B2076" t="s">
-        <v>211</v>
+        <v>3267</v>
       </c>
       <c r="C2076" t="s">
-        <v>735</v>
+        <v>103</v>
       </c>
       <c r="D2076" t="s">
         <v>13</v>
       </c>
       <c r="E2076" t="s">
-        <v>3259</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="2077">
       <c r="A2077" t="s">
-        <v>3260</v>
+        <v>3268</v>
       </c>
       <c r="B2077" t="s">
-        <v>291</v>
+        <v>3269</v>
       </c>
       <c r="C2077" t="s">
-        <v>103</v>
+        <v>555</v>
       </c>
       <c r="D2077" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2077" t="s">
-        <v>3261</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="2078">
       <c r="A2078" t="s">
-        <v>3262</v>
+        <v>3271</v>
       </c>
       <c r="B2078" t="s">
-        <v>3262</v>
+        <v>3272</v>
       </c>
       <c r="C2078" t="s">
-        <v>1935</v>
+        <v>455</v>
       </c>
       <c r="D2078" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E2078" t="s">
-        <v>3263</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="2079">
       <c r="A2079" t="s">
-        <v>3262</v>
+        <v>3271</v>
       </c>
       <c r="B2079" t="s">
-        <v>3262</v>
+        <v>3272</v>
       </c>
       <c r="C2079" t="s">
-        <v>922</v>
+        <v>458</v>
       </c>
       <c r="D2079" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E2079" t="s">
-        <v>3263</v>
+        <v>3274</v>
       </c>
     </row>
     <row r="2080">
       <c r="A2080" t="s">
-        <v>3264</v>
+        <v>3275</v>
       </c>
       <c r="B2080" t="s">
-        <v>3265</v>
+        <v>291</v>
       </c>
       <c r="C2080" t="s">
-        <v>373</v>
+        <v>115</v>
       </c>
       <c r="D2080" t="s">
         <v>13</v>
       </c>
       <c r="E2080" t="s">
-        <v>3266</v>
+        <v>3276</v>
       </c>
     </row>
     <row r="2081">
       <c r="A2081" t="s">
-        <v>3264</v>
+        <v>3277</v>
       </c>
       <c r="B2081" t="s">
-        <v>3267</v>
+        <v>3277</v>
       </c>
       <c r="C2081" t="s">
-        <v>103</v>
+        <v>399</v>
       </c>
       <c r="D2081" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2081" t="s">
-        <v>3266</v>
+        <v>3278</v>
       </c>
     </row>
     <row r="2082">
       <c r="A2082" t="s">
-        <v>3268</v>
+        <v>3277</v>
       </c>
       <c r="B2082" t="s">
-        <v>3269</v>
+        <v>3277</v>
       </c>
       <c r="C2082" t="s">
-        <v>555</v>
+        <v>49</v>
       </c>
       <c r="D2082" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E2082" t="s">
-        <v>3270</v>
+        <v>3278</v>
       </c>
     </row>
     <row r="2083">
       <c r="A2083" t="s">
-        <v>3271</v>
+        <v>3279</v>
       </c>
       <c r="B2083" t="s">
-        <v>3272</v>
+        <v>191</v>
       </c>
       <c r="C2083" t="s">
-        <v>455</v>
+        <v>57</v>
       </c>
       <c r="D2083" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2083" t="s">
-        <v>3273</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="2084">
       <c r="A2084" t="s">
-        <v>3271</v>
+        <v>3281</v>
       </c>
       <c r="B2084" t="s">
-        <v>3272</v>
+        <v>191</v>
       </c>
       <c r="C2084" t="s">
-        <v>458</v>
+        <v>31</v>
       </c>
       <c r="D2084" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2084" t="s">
-        <v>3274</v>
+        <v>3282</v>
       </c>
     </row>
     <row r="2085">
       <c r="A2085" t="s">
-        <v>3275</v>
+        <v>3281</v>
       </c>
       <c r="B2085" t="s">
-        <v>291</v>
+        <v>191</v>
       </c>
       <c r="C2085" t="s">
-        <v>115</v>
+        <v>799</v>
       </c>
       <c r="D2085" t="s">
         <v>13</v>
       </c>
       <c r="E2085" t="s">
-        <v>3276</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="2086">
       <c r="A2086" t="s">
-        <v>3277</v>
+        <v>3284</v>
       </c>
       <c r="B2086" t="s">
-        <v>3277</v>
+        <v>3285</v>
       </c>
       <c r="C2086" t="s">
-        <v>399</v>
+        <v>117</v>
       </c>
       <c r="D2086" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2086" t="s">
-        <v>3278</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="2087">
       <c r="A2087" t="s">
-        <v>3277</v>
+        <v>3287</v>
       </c>
       <c r="B2087" t="s">
-        <v>3277</v>
+        <v>3285</v>
       </c>
       <c r="C2087" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D2087" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2087" t="s">
-        <v>3278</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="2088">
       <c r="A2088" t="s">
-        <v>3279</v>
+        <v>3289</v>
       </c>
       <c r="B2088" t="s">
-        <v>191</v>
+        <v>2118</v>
       </c>
       <c r="C2088" t="s">
-        <v>57</v>
+        <v>378</v>
       </c>
       <c r="D2088" t="s">
         <v>13</v>
       </c>
       <c r="E2088" t="s">
-        <v>3280</v>
-      </c>
-    </row>
-    <row r="2089">
-      <c r="A2089" t="s">
-        <v>3281</v>
-      </c>
-      <c r="B2089" t="s">
-        <v>191</v>
-      </c>
-      <c r="C2089" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2089" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2089" t="s">
-        <v>3282</v>
-      </c>
-    </row>
-    <row r="2090">
-      <c r="A2090" t="s">
-        <v>3281</v>
-      </c>
-      <c r="B2090" t="s">
-        <v>191</v>
-      </c>
-      <c r="C2090" t="s">
-        <v>799</v>
-      </c>
-      <c r="D2090" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2090" t="s">
-        <v>3283</v>
-      </c>
-    </row>
-    <row r="2091">
-      <c r="A2091" t="s">
-        <v>3284</v>
-      </c>
-      <c r="B2091" t="s">
-        <v>3285</v>
-      </c>
-      <c r="C2091" t="s">
-        <v>117</v>
-      </c>
-      <c r="D2091" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2091" t="s">
-        <v>3286</v>
-      </c>
-    </row>
-    <row r="2092">
-      <c r="A2092" t="s">
-        <v>3287</v>
-      </c>
-      <c r="B2092" t="s">
-        <v>3285</v>
-      </c>
-      <c r="C2092" t="s">
-        <v>117</v>
-      </c>
-      <c r="D2092" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2092" t="s">
-        <v>3288</v>
-      </c>
-    </row>
-    <row r="2093">
-      <c r="A2093" t="s">
-        <v>3289</v>
-      </c>
-      <c r="B2093" t="s">
-        <v>2118</v>
-      </c>
-      <c r="C2093" t="s">
-        <v>378</v>
-      </c>
-      <c r="D2093" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2093" t="s">
         <v>3290</v>
       </c>
     </row>
@@ -55950,7 +55868,7 @@
         <v>1606</v>
       </c>
       <c r="B145" t="s">
-        <v>4042</v>
+        <v>4071</v>
       </c>
       <c r="C145" t="s">
         <v>1607</v>
@@ -56024,7 +55942,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>4071</v>
+        <v>4072</v>
       </c>
       <c r="B152" t="s">
         <v>8</v>
@@ -56079,7 +55997,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>4072</v>
+        <v>4073</v>
       </c>
       <c r="B157" t="s">
         <v>8</v>
@@ -56159,7 +56077,7 @@
         <v>1207</v>
       </c>
       <c r="B164" t="s">
-        <v>4073</v>
+        <v>4074</v>
       </c>
       <c r="C164" t="s">
         <v>1211</v>
@@ -56250,7 +56168,7 @@
         <v>8</v>
       </c>
       <c r="C172" t="s">
-        <v>4074</v>
+        <v>4075</v>
       </c>
     </row>
     <row r="173">
@@ -56272,7 +56190,7 @@
         <v>4014</v>
       </c>
       <c r="C174" t="s">
-        <v>4075</v>
+        <v>4076</v>
       </c>
     </row>
     <row r="175">
@@ -56291,10 +56209,10 @@
         <v>1356</v>
       </c>
       <c r="B176" t="s">
-        <v>4076</v>
+        <v>4077</v>
       </c>
       <c r="C176" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="177">
@@ -56321,13 +56239,13 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>4078</v>
+        <v>4079</v>
       </c>
       <c r="B179" t="s">
         <v>4044</v>
       </c>
       <c r="C179" t="s">
-        <v>4079</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="180">
@@ -56360,7 +56278,7 @@
         <v>4062</v>
       </c>
       <c r="C182" t="s">
-        <v>4080</v>
+        <v>4081</v>
       </c>
     </row>
     <row r="183">
@@ -56368,10 +56286,10 @@
         <v>1434</v>
       </c>
       <c r="B183" t="s">
-        <v>4081</v>
+        <v>4082</v>
       </c>
       <c r="C183" t="s">
-        <v>4082</v>
+        <v>4083</v>
       </c>
     </row>
     <row r="184">
@@ -56379,10 +56297,10 @@
         <v>1485</v>
       </c>
       <c r="B184" t="s">
-        <v>4083</v>
+        <v>4084</v>
       </c>
       <c r="C184" t="s">
-        <v>4084</v>
+        <v>4085</v>
       </c>
     </row>
     <row r="185">
@@ -56393,7 +56311,7 @@
         <v>4010</v>
       </c>
       <c r="C185" t="s">
-        <v>4085</v>
+        <v>4086</v>
       </c>
     </row>
     <row r="186">
@@ -56423,7 +56341,7 @@
         <v>1464</v>
       </c>
       <c r="B188" t="s">
-        <v>4086</v>
+        <v>4087</v>
       </c>
       <c r="C188" t="s">
         <v>1465</v>
@@ -56566,7 +56484,7 @@
         <v>1566</v>
       </c>
       <c r="B201" t="s">
-        <v>4087</v>
+        <v>4088</v>
       </c>
       <c r="C201" t="s">
         <v>1567</v>
@@ -56580,7 +56498,7 @@
         <v>4069</v>
       </c>
       <c r="C202" t="s">
-        <v>4088</v>
+        <v>4089</v>
       </c>
     </row>
     <row r="203">
@@ -56602,7 +56520,7 @@
         <v>4010</v>
       </c>
       <c r="C204" t="s">
-        <v>4089</v>
+        <v>4090</v>
       </c>
     </row>
     <row r="205">
@@ -56709,10 +56627,10 @@
         <v>1683</v>
       </c>
       <c r="B214" t="s">
-        <v>4090</v>
+        <v>4091</v>
       </c>
       <c r="C214" t="s">
-        <v>4091</v>
+        <v>4092</v>
       </c>
     </row>
     <row r="215">
@@ -56800,7 +56718,7 @@
         <v>4012</v>
       </c>
       <c r="C222" t="s">
-        <v>4092</v>
+        <v>4093</v>
       </c>
     </row>
     <row r="223">
@@ -56860,13 +56778,13 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>4093</v>
+        <v>4094</v>
       </c>
       <c r="B228" t="s">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="C228" t="s">
-        <v>4095</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="229">
@@ -56877,7 +56795,7 @@
         <v>4053</v>
       </c>
       <c r="C229" t="s">
-        <v>4096</v>
+        <v>4097</v>
       </c>
     </row>
     <row r="230">
@@ -56954,7 +56872,7 @@
         <v>4027</v>
       </c>
       <c r="C236" t="s">
-        <v>4097</v>
+        <v>4098</v>
       </c>
     </row>
     <row r="237">
@@ -57009,7 +56927,7 @@
         <v>4010</v>
       </c>
       <c r="C241" t="s">
-        <v>4098</v>
+        <v>4099</v>
       </c>
     </row>
     <row r="242">
@@ -57028,10 +56946,10 @@
         <v>1413</v>
       </c>
       <c r="B243" t="s">
-        <v>4099</v>
+        <v>4100</v>
       </c>
       <c r="C243" t="s">
-        <v>4100</v>
+        <v>4101</v>
       </c>
     </row>
     <row r="244">
@@ -57105,7 +57023,7 @@
         <v>1960</v>
       </c>
       <c r="B250" t="s">
-        <v>4101</v>
+        <v>4102</v>
       </c>
       <c r="C250" t="s">
         <v>1961</v>
@@ -57262,7 +57180,7 @@
         <v>4008</v>
       </c>
       <c r="C264" t="s">
-        <v>4102</v>
+        <v>4103</v>
       </c>
     </row>
     <row r="265">
@@ -57281,7 +57199,7 @@
         <v>2067</v>
       </c>
       <c r="B266" t="s">
-        <v>4083</v>
+        <v>4084</v>
       </c>
       <c r="C266" t="s">
         <v>2068</v>
@@ -57292,7 +57210,7 @@
         <v>2069</v>
       </c>
       <c r="B267" t="s">
-        <v>4083</v>
+        <v>4084</v>
       </c>
       <c r="C267" t="s">
         <v>2070</v>
@@ -57303,7 +57221,7 @@
         <v>2071</v>
       </c>
       <c r="B268" t="s">
-        <v>4103</v>
+        <v>4104</v>
       </c>
       <c r="C268" t="s">
         <v>2072</v>
@@ -57314,7 +57232,7 @@
         <v>2073</v>
       </c>
       <c r="B269" t="s">
-        <v>4104</v>
+        <v>4105</v>
       </c>
       <c r="C269" t="s">
         <v>2074</v>
@@ -57328,7 +57246,7 @@
         <v>4069</v>
       </c>
       <c r="C270" t="s">
-        <v>4105</v>
+        <v>4106</v>
       </c>
     </row>
     <row r="271">
@@ -57339,7 +57257,7 @@
         <v>4054</v>
       </c>
       <c r="C271" t="s">
-        <v>4106</v>
+        <v>4107</v>
       </c>
     </row>
     <row r="272">
@@ -57347,10 +57265,10 @@
         <v>1216</v>
       </c>
       <c r="B272" t="s">
-        <v>4107</v>
+        <v>4108</v>
       </c>
       <c r="C272" t="s">
-        <v>4108</v>
+        <v>4109</v>
       </c>
     </row>
     <row r="273">
@@ -57358,7 +57276,7 @@
         <v>2076</v>
       </c>
       <c r="B273" t="s">
-        <v>4109</v>
+        <v>4110</v>
       </c>
       <c r="C273" t="s">
         <v>2077</v>
@@ -57369,10 +57287,10 @@
         <v>2080</v>
       </c>
       <c r="B274" t="s">
-        <v>4109</v>
+        <v>4110</v>
       </c>
       <c r="C274" t="s">
-        <v>4110</v>
+        <v>4111</v>
       </c>
     </row>
     <row r="275">
@@ -57383,7 +57301,7 @@
         <v>4010</v>
       </c>
       <c r="C275" t="s">
-        <v>4111</v>
+        <v>4112</v>
       </c>
     </row>
     <row r="276">
@@ -57446,10 +57364,10 @@
         <v>2172</v>
       </c>
       <c r="B281" t="s">
-        <v>4112</v>
+        <v>4113</v>
       </c>
       <c r="C281" t="s">
-        <v>4113</v>
+        <v>4114</v>
       </c>
     </row>
     <row r="282">
@@ -57504,7 +57422,7 @@
         <v>4042</v>
       </c>
       <c r="C286" t="s">
-        <v>4114</v>
+        <v>4115</v>
       </c>
     </row>
     <row r="287">
@@ -57567,7 +57485,7 @@
         <v>2247</v>
       </c>
       <c r="B292" t="s">
-        <v>4115</v>
+        <v>4116</v>
       </c>
       <c r="C292" t="s">
         <v>2248</v>
@@ -57669,7 +57587,7 @@
         <v>4014</v>
       </c>
       <c r="C301" t="s">
-        <v>4116</v>
+        <v>4117</v>
       </c>
     </row>
     <row r="302">
@@ -57680,7 +57598,7 @@
         <v>4006</v>
       </c>
       <c r="C302" t="s">
-        <v>4117</v>
+        <v>4118</v>
       </c>
     </row>
     <row r="303">
@@ -57713,7 +57631,7 @@
         <v>4006</v>
       </c>
       <c r="C305" t="s">
-        <v>4118</v>
+        <v>4119</v>
       </c>
     </row>
     <row r="306">
@@ -57875,7 +57793,7 @@
         <v>2433</v>
       </c>
       <c r="B320" t="s">
-        <v>4119</v>
+        <v>4120</v>
       </c>
       <c r="C320" t="s">
         <v>2434</v>
@@ -57897,10 +57815,10 @@
         <v>2439</v>
       </c>
       <c r="B322" t="s">
-        <v>4119</v>
+        <v>4120</v>
       </c>
       <c r="C322" t="s">
-        <v>4120</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="323">
@@ -57911,7 +57829,7 @@
         <v>4042</v>
       </c>
       <c r="C323" t="s">
-        <v>4121</v>
+        <v>4122</v>
       </c>
     </row>
     <row r="324">
@@ -57922,7 +57840,7 @@
         <v>4010</v>
       </c>
       <c r="C324" t="s">
-        <v>4122</v>
+        <v>4123</v>
       </c>
     </row>
     <row r="325">
@@ -57930,7 +57848,7 @@
         <v>2446</v>
       </c>
       <c r="B325" t="s">
-        <v>4101</v>
+        <v>4102</v>
       </c>
       <c r="C325" t="s">
         <v>2447</v>
@@ -57941,7 +57859,7 @@
         <v>12</v>
       </c>
       <c r="B326" t="s">
-        <v>4123</v>
+        <v>4124</v>
       </c>
       <c r="C326" t="s">
         <v>2448</v>
@@ -57977,7 +57895,7 @@
         <v>4062</v>
       </c>
       <c r="C329" t="s">
-        <v>4124</v>
+        <v>4125</v>
       </c>
     </row>
     <row r="330">
@@ -58032,7 +57950,7 @@
         <v>4044</v>
       </c>
       <c r="C334" t="s">
-        <v>4125</v>
+        <v>4126</v>
       </c>
     </row>
     <row r="335">
@@ -58076,7 +57994,7 @@
         <v>4039</v>
       </c>
       <c r="C338" t="s">
-        <v>4126</v>
+        <v>4127</v>
       </c>
     </row>
     <row r="339">
@@ -58120,7 +58038,7 @@
         <v>4027</v>
       </c>
       <c r="C342" t="s">
-        <v>4127</v>
+        <v>4128</v>
       </c>
     </row>
     <row r="343">
@@ -58139,7 +58057,7 @@
         <v>1968</v>
       </c>
       <c r="B344" t="s">
-        <v>4119</v>
+        <v>4120</v>
       </c>
       <c r="C344" t="s">
         <v>3808</v>
@@ -58219,7 +58137,7 @@
         <v>4010</v>
       </c>
       <c r="C351" t="s">
-        <v>4128</v>
+        <v>4129</v>
       </c>
     </row>
     <row r="352">
@@ -58238,7 +58156,7 @@
         <v>549</v>
       </c>
       <c r="B353" t="s">
-        <v>4129</v>
+        <v>4130</v>
       </c>
       <c r="C353" t="s">
         <v>2618</v>
@@ -58274,7 +58192,7 @@
         <v>4014</v>
       </c>
       <c r="C356" t="s">
-        <v>4130</v>
+        <v>4131</v>
       </c>
     </row>
     <row r="357">
@@ -58285,7 +58203,7 @@
         <v>4008</v>
       </c>
       <c r="C357" t="s">
-        <v>4131</v>
+        <v>4132</v>
       </c>
     </row>
     <row r="358">
@@ -58296,7 +58214,7 @@
         <v>4055</v>
       </c>
       <c r="C358" t="s">
-        <v>4132</v>
+        <v>4133</v>
       </c>
     </row>
     <row r="359">
@@ -58337,10 +58255,10 @@
         <v>2677</v>
       </c>
       <c r="B362" t="s">
-        <v>4104</v>
+        <v>4105</v>
       </c>
       <c r="C362" t="s">
-        <v>4133</v>
+        <v>4134</v>
       </c>
     </row>
     <row r="363">
@@ -58373,7 +58291,7 @@
         <v>4044</v>
       </c>
       <c r="C365" t="s">
-        <v>4134</v>
+        <v>4135</v>
       </c>
     </row>
     <row r="366">
@@ -58384,7 +58302,7 @@
         <v>8</v>
       </c>
       <c r="C366" t="s">
-        <v>4135</v>
+        <v>4136</v>
       </c>
     </row>
     <row r="367">
@@ -58505,7 +58423,7 @@
         <v>4012</v>
       </c>
       <c r="C377" t="s">
-        <v>4136</v>
+        <v>4137</v>
       </c>
     </row>
     <row r="378">
@@ -58615,7 +58533,7 @@
         <v>4008</v>
       </c>
       <c r="C387" t="s">
-        <v>4137</v>
+        <v>4138</v>
       </c>
     </row>
     <row r="388">
@@ -58656,7 +58574,7 @@
         <v>3178</v>
       </c>
       <c r="B391" t="s">
-        <v>4138</v>
+        <v>4139</v>
       </c>
       <c r="C391" t="s">
         <v>3179</v>
@@ -58703,7 +58621,7 @@
         <v>4014</v>
       </c>
       <c r="C395" t="s">
-        <v>4139</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="396">
@@ -58714,7 +58632,7 @@
         <v>8</v>
       </c>
       <c r="C396" t="s">
-        <v>4140</v>
+        <v>4141</v>
       </c>
     </row>
     <row r="397">
@@ -58766,7 +58684,7 @@
         <v>3219</v>
       </c>
       <c r="B401" t="s">
-        <v>4103</v>
+        <v>4104</v>
       </c>
       <c r="C401" t="s">
         <v>3221</v>
@@ -58780,7 +58698,7 @@
         <v>8</v>
       </c>
       <c r="C402" t="s">
-        <v>4141</v>
+        <v>4142</v>
       </c>
     </row>
     <row r="403">
@@ -58846,7 +58764,7 @@
         <v>4053</v>
       </c>
       <c r="C408" t="s">
-        <v>4096</v>
+        <v>4097</v>
       </c>
     </row>
     <row r="409">
@@ -58854,10 +58772,10 @@
         <v>719</v>
       </c>
       <c r="B409" t="s">
-        <v>4142</v>
+        <v>4143</v>
       </c>
       <c r="C409" t="s">
-        <v>4143</v>
+        <v>4144</v>
       </c>
     </row>
     <row r="410">
@@ -58898,10 +58816,10 @@
         <v>3277</v>
       </c>
       <c r="B413" t="s">
-        <v>4144</v>
+        <v>4145</v>
       </c>
       <c r="C413" t="s">
-        <v>4145</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="414">
@@ -58912,7 +58830,7 @@
         <v>4044</v>
       </c>
       <c r="C414" t="s">
-        <v>4146</v>
+        <v>4147</v>
       </c>
     </row>
   </sheetData>
